--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.748627775838305</v>
+        <v>9.748635144069061</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.723752235354221</v>
+        <v>9.72376843548817</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.720682691944798</v>
+        <v>9.720705027081154</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.699918460349625</v>
+        <v>9.699954005963319</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.704434194124415</v>
+        <v>9.704469377436785</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.697685289991899</v>
+        <v>9.697720031604193</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.693507969725866</v>
+        <v>9.693542882600161</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.707556780412339</v>
+        <v>9.707592569348549</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.720073227077886</v>
+        <v>9.720115138193743</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.726941238037284</v>
+        <v>9.726973579220971</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.735592098293354</v>
+        <v>9.735624838145455</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.711985820173588</v>
+        <v>9.712017880569997</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.667599232836935</v>
+        <v>9.667631375551485</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.633420416161568</v>
+        <v>9.633460531109879</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.60031539013313</v>
+        <v>9.600342192804993</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.562484223753113</v>
+        <v>9.562507641763894</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.504400492923331</v>
+        <v>9.504451503124656</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.432696592610315</v>
+        <v>9.432767644027775</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.356827755599804</v>
+        <v>9.356894127662176</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.289344799099631</v>
+        <v>9.289414382968733</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.266629885516199</v>
+        <v>9.266677735992431</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.279387391523883</v>
+        <v>9.279423816206497</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.239244491943554</v>
+        <v>9.239212756581935</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.170279551844729</v>
+        <v>9.170213206722451</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.106098539776211</v>
+        <v>9.105996352544169</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.011740203346863</v>
+        <v>9.011617318164003</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.940919564766633</v>
+        <v>8.940768491942309</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.937809454791473</v>
+        <v>8.937621747543336</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.947421490149447</v>
+        <v>8.947204549419537</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.072057579964898</v>
+        <v>9.071754636392056</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.125849489554756</v>
+        <v>9.125532791073205</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.291882716600716</v>
+        <v>9.291633787712067</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.385062141363665</v>
+        <v>9.384867300981508</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.404189141886107</v>
+        <v>9.404024677074293</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.487978045553497</v>
+        <v>9.487837318864795</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.607587784107515</v>
+        <v>9.6076296835307</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.599112398599924</v>
+        <v>9.59921869458891</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.61704438527453</v>
+        <v>9.617260747672198</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.615396626778153</v>
+        <v>9.615756840864712</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.596765434439678</v>
+        <v>9.597178770463724</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.632366955747599</v>
+        <v>9.632831962045453</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.499679228047544</v>
+        <v>9.500091607575914</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.431564537316429</v>
+        <v>9.431957459624442</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.283489346758552</v>
+        <v>9.283710046511668</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.186732375017447</v>
+        <v>9.186872213839415</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.076387911147666</v>
+        <v>9.076346010107965</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.049137787557768</v>
+        <v>9.049042168064222</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.046290682345209</v>
+        <v>9.046214214497374</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.020738460207511</v>
+        <v>9.020621975253427</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>9.0004234421439</v>
+        <v>9.000304948286933</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.012061923153922</v>
+        <v>9.0120041200971</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.039396284029989</v>
+        <v>9.039417718407574</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.059081253001995</v>
+        <v>9.059146045866054</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.060771130667474</v>
+        <v>9.0607728536921</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.047736244273624</v>
+        <v>9.047723250871336</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.038773310279577</v>
+        <v>9.038734813948768</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.046584120722809</v>
+        <v>9.046496645877522</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.062416893629912</v>
+        <v>9.062283961818862</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.074564825945071</v>
+        <v>9.074362015946715</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.08907383397456</v>
+        <v>9.088914590226635</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.073135576968106</v>
+        <v>9.072891510824121</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>9.056235443844706</v>
+        <v>9.056128345991464</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>9.04504199725883</v>
+        <v>9.045237620316492</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>9.045883602366183</v>
+        <v>9.045797595953646</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>9.045567027057766</v>
+        <v>9.045460592763867</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>9.040034208037754</v>
+        <v>9.040069346325744</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>9.039571500646911</v>
+        <v>9.039750652501803</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>9.029522142268695</v>
+        <v>9.030106027041827</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>9.036397305382522</v>
+        <v>9.036586785243824</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>9.038186095079737</v>
+        <v>9.037418724223837</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>9.052888751432723</v>
+        <v>9.04991682697295</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>9.070232417937531</v>
+        <v>9.063597160391726</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>9.024285654891738</v>
+        <v>9.016845636671553</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>8.996708320824576</v>
+        <v>8.986535170475504</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B115"/>
+  <dimension ref="A1:B116"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.748635144069061</v>
+        <v>9.748642357196541</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.72376843548817</v>
+        <v>9.723784294826213</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.720705027081154</v>
+        <v>9.720726893225287</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.699954005963319</v>
+        <v>9.699988804177789</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.704469377436785</v>
+        <v>9.704503820821586</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.697720031604193</v>
+        <v>9.697754042519156</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.693542882600161</v>
+        <v>9.693577060722713</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.707592569348549</v>
+        <v>9.707627604009238</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.720115138193743</v>
+        <v>9.720156168922456</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.726973579220971</v>
+        <v>9.727005242099919</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.735624838145455</v>
+        <v>9.73565689133479</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.712017880569997</v>
+        <v>9.712049268685423</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.667631375551485</v>
+        <v>9.667662848171497</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.633460531109879</v>
+        <v>9.633499809915897</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.600342192804993</v>
+        <v>9.600368439129774</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.562507641763894</v>
+        <v>9.562530569282167</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.504451503124656</v>
+        <v>9.504501440990975</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.432767644027775</v>
+        <v>9.432837210129765</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.356894127662176</v>
+        <v>9.356959110453793</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.289414382968733</v>
+        <v>9.289482516882234</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.266677735992431</v>
+        <v>9.266724629198741</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.279423816206497</v>
+        <v>9.279459542219573</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.239212756581935</v>
+        <v>9.239181742246867</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.170213206722451</v>
+        <v>9.170148320528567</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.105996352544169</v>
+        <v>9.105896390853648</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.011617318164003</v>
+        <v>9.01149710157485</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.940768491942309</v>
+        <v>8.940620689381792</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.937621747543336</v>
+        <v>8.9374380830204</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.947204549419537</v>
+        <v>8.946992189520913</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.071754636392056</v>
+        <v>9.07145803943083</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.125532791073205</v>
+        <v>9.125222724962788</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.291633787712067</v>
+        <v>9.291389971936466</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.384867300981508</v>
+        <v>9.384676431533798</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.404024677074293</v>
+        <v>9.403863488207437</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.487837318864795</v>
+        <v>9.487699320869487</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.6076296835307</v>
+        <v>9.607670497478273</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.59921869458891</v>
+        <v>9.599322511375643</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.617260747672198</v>
+        <v>9.617472359256503</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.615756840864712</v>
+        <v>9.61610943528105</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.597178770463724</v>
+        <v>9.597583414092435</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.632831962045453</v>
+        <v>9.63328725794498</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.500091607575914</v>
+        <v>9.500495545407821</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.431957459624442</v>
+        <v>9.432342430115114</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.283710046511668</v>
+        <v>9.283926378826052</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.186872213839415</v>
+        <v>9.187009346707089</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.076346010107965</v>
+        <v>9.076305047283665</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.049042168064222</v>
+        <v>9.048948518050613</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.046214214497374</v>
+        <v>9.04613930523681</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.020621975253427</v>
+        <v>9.020507801631258</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>9.000304948286933</v>
+        <v>9.000188746200742</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.0120041200971</v>
+        <v>9.011947369934216</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.039417718407574</v>
+        <v>9.039438637833882</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.059146045866054</v>
+        <v>9.059209535525314</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.0607728536921</v>
+        <v>9.060774692939502</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.047723250871336</v>
+        <v>9.047710592539115</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.038734813948768</v>
+        <v>9.03869712714647</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.046496645877522</v>
+        <v>9.046410896244218</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.062283961818862</v>
+        <v>9.062153551649942</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.074362015946715</v>
+        <v>9.074162991250518</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.088914590226635</v>
+        <v>9.088758411638608</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.072891510824121</v>
+        <v>9.072753796429291</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>9.056128345991464</v>
+        <v>9.056764964434588</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>9.045237620316492</v>
+        <v>9.046135583848823</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>9.045797595953646</v>
+        <v>9.046855406442265</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>9.045460592763867</v>
+        <v>9.046570168154117</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>9.040069346325744</v>
+        <v>9.041327219198397</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>9.039750652501803</v>
+        <v>9.04111206920858</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>9.030106027041827</v>
+        <v>9.031932693808541</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>9.036586785243824</v>
+        <v>9.038179382027876</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>9.037418724223837</v>
+        <v>9.038437085270242</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>9.04991682697295</v>
+        <v>9.049298237336933</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>9.063597160391726</v>
+        <v>9.060298083336775</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>9.016845636671553</v>
+        <v>9.014111809129748</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,15 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>8.986535170475504</v>
+        <v>8.984916645962294</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116" s="3">
+        <v>46367</v>
+      </c>
+      <c r="B116">
+        <v>8.972783802939617</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.748642357196541</v>
+        <v>9.748649420067011</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.723784294826213</v>
+        <v>9.723799824009427</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.720726893225287</v>
+        <v>9.720748304993627</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.699988804177789</v>
+        <v>9.700022878316364</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.704503820821586</v>
+        <v>9.704537547373491</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.697754042519156</v>
+        <v>9.697787345545162</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.693577060722713</v>
+        <v>9.693610527042425</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.707627604009238</v>
+        <v>9.707661907986717</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.720156168922456</v>
+        <v>9.720196346707205</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.727005242099919</v>
+        <v>9.727036247787186</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.73565689133479</v>
+        <v>9.735688279234427</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.712049268685423</v>
+        <v>9.712080005441234</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.667662848171497</v>
+        <v>9.66769367142733</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.633499809915897</v>
+        <v>9.633538278440922</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.600368439129774</v>
+        <v>9.600394146243168</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.562530569282167</v>
+        <v>9.562553021553672</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.504501440990975</v>
+        <v>9.504550339969409</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.432837210129765</v>
+        <v>9.432905336976223</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.356959110453793</v>
+        <v>9.357022747114355</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.289482516882234</v>
+        <v>9.289549245669249</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.266724629198741</v>
+        <v>9.266770593483262</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.279459542219573</v>
+        <v>9.279494589279807</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.239181742246867</v>
+        <v>9.239151424804197</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.170148320528567</v>
+        <v>9.170084845818836</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.105896390853648</v>
+        <v>9.105798582972355</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.01149710157485</v>
+        <v>9.01137946781629</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.940620689381792</v>
+        <v>8.940476052315786</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.9374380830204</v>
+        <v>8.937258332350901</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.946992189520913</v>
+        <v>8.946784267078272</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.07145803943083</v>
+        <v>9.071167592000213</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.125222724962788</v>
+        <v>9.124919085346473</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.291389971936466</v>
+        <v>9.291151113671983</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.384676431533798</v>
+        <v>9.384489413189048</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.403863488207437</v>
+        <v>9.403705478883976</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.487699320869487</v>
+        <v>9.487563973719604</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.607670497478273</v>
+        <v>9.607710266075607</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.599322511375643</v>
+        <v>9.599423933690261</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.617472359256503</v>
+        <v>9.617679374162728</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.61610943528105</v>
+        <v>9.616454648818513</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.597583414092435</v>
+        <v>9.597979636077755</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.63328725794498</v>
+        <v>9.633733143921324</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.500495545407821</v>
+        <v>9.500891297556439</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.432342430115114</v>
+        <v>9.432719687015432</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.283926378826052</v>
+        <v>9.284138471403054</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.187009346707089</v>
+        <v>9.187143850863237</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.076305047283665</v>
+        <v>9.076264991814549</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.048948518050613</v>
+        <v>9.048856777520569</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.04613930523681</v>
+        <v>9.046065907632087</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.020507801631258</v>
+        <v>9.020395871586006</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>9.000188746200742</v>
+        <v>9.000074770541023</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.011947369934216</v>
+        <v>9.011891644731465</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.039438637833882</v>
+        <v>9.039459060244074</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.059209535525314</v>
+        <v>9.059271760702881</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.060774692939502</v>
+        <v>9.060776640200086</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.047710592539115</v>
+        <v>9.047698257328772</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.03869712714647</v>
+        <v>9.038660225051888</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.046410896244218</v>
+        <v>9.046326821982365</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.062153551649942</v>
+        <v>9.062025593239747</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.074162991250518</v>
+        <v>9.073967648715334</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.088758411638608</v>
+        <v>9.088605212239834</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.072753796429291</v>
+        <v>9.072618517146223</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>9.056764964434588</v>
+        <v>9.05722332586482</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>9.046135583848823</v>
+        <v>9.046821803663239</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>9.046855406442265</v>
+        <v>9.047647068637232</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>9.046570168154117</v>
+        <v>9.047346879075761</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>9.041327219198397</v>
+        <v>9.042235950845555</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>9.04111206920858</v>
+        <v>9.042085466588246</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>9.031932693808541</v>
+        <v>9.033283735279824</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>9.038179382027876</v>
+        <v>9.039233043845268</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>9.038437085270242</v>
+        <v>9.038898247840432</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>9.049298237336933</v>
+        <v>9.048127859470604</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>9.060298083336775</v>
+        <v>9.056576110055897</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>9.014111809129748</v>
+        <v>9.010716714808527</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>8.984916645962294</v>
+        <v>8.981887294035907</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>8.972783802939617</v>
+        <v>8.964614077999009</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.748649420067011</v>
+        <v>9.748656337326924</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.723799824009427</v>
+        <v>9.723815033240474</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.720748304993627</v>
+        <v>9.720769276401551</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.700022878316364</v>
+        <v>9.700056250742097</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.704537547373491</v>
+        <v>9.704570579236128</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.697787345545162</v>
+        <v>9.697819962551257</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.693610527042425</v>
+        <v>9.693643303562521</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.707661907986717</v>
+        <v>9.707695503899721</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.720196346707205</v>
+        <v>9.720235697862661</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.727036247787186</v>
+        <v>9.72706661652882</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.735688279234427</v>
+        <v>9.735719022339758</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.712080005441234</v>
+        <v>9.712110110899838</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.66769367142733</v>
+        <v>9.6677238652033</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.633538278440922</v>
+        <v>9.633575961491122</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.600394146243168</v>
+        <v>9.600419330584661</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.562553021553672</v>
+        <v>9.56257501319898</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.504550339969409</v>
+        <v>9.504598232131009</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.432905336976223</v>
+        <v>9.432972068743497</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.357022747114355</v>
+        <v>9.357085079016883</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.289549245669249</v>
+        <v>9.289614612330713</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.266770593483262</v>
+        <v>9.266815656089687</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.279494589279807</v>
+        <v>9.279528976377488</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.239151424804197</v>
+        <v>9.23912178117893</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.170084845818836</v>
+        <v>9.170022737178169</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.105798582972355</v>
+        <v>9.105702860210542</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.01137946781629</v>
+        <v>9.011264334752255</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.940476052315786</v>
+        <v>8.940334480392044</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.937258332350901</v>
+        <v>8.937082372069499</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.946784267078272</v>
+        <v>8.946580644629858</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.071167592000213</v>
+        <v>9.070883105083729</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.124919085346473</v>
+        <v>9.124621674768374</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.291151113671983</v>
+        <v>9.29091706355322</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.384489413189048</v>
+        <v>9.384306130875279</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.403705478883976</v>
+        <v>9.403550556426264</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.487563973719604</v>
+        <v>9.487431202467683</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.607710266075607</v>
+        <v>9.607749027544173</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.599423933690261</v>
+        <v>9.59952304248195</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.617679374162728</v>
+        <v>9.617881939954565</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.616454648818513</v>
+        <v>9.616792710411664</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.597979636077755</v>
+        <v>9.598367696066568</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.633733143921324</v>
+        <v>9.63416990820123</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.500891297556439</v>
+        <v>9.501279109809829</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.432719687015432</v>
+        <v>9.433089459161305</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.284138471403054</v>
+        <v>9.284346447041795</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.187143850863237</v>
+        <v>9.187275800661515</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.076264991814549</v>
+        <v>9.076225814168012</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.048856777520569</v>
+        <v>9.048766888880666</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.046065907632087</v>
+        <v>9.045993976607443</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.020395871586006</v>
+        <v>9.020286119970132</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>9.000074770541023</v>
+        <v>8.99996295840274</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.011891644731465</v>
+        <v>9.011836917508795</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.039459060244074</v>
+        <v>9.039479002763736</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.059271760702881</v>
+        <v>9.059332758611298</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.060776640200086</v>
+        <v>9.060778687783095</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.047698257328772</v>
+        <v>9.04768623382787</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.038660225051888</v>
+        <v>9.038624083831273</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.046326821982365</v>
+        <v>9.046244375124591</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.062025593239747</v>
+        <v>9.061900019214701</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.073967648715334</v>
+        <v>9.073775888838824</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.088605212239834</v>
+        <v>9.088454909174645</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.072618517146223</v>
+        <v>9.072485612049242</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>9.05722332586482</v>
+        <v>9.057782251417041</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>9.046821803663239</v>
+        <v>9.0476285998951</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>9.047647068637232</v>
+        <v>9.048564808582491</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>9.047346879075761</v>
+        <v>9.048243936928319</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>9.042235950845555</v>
+        <v>9.043275352223763</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>9.042085466588246</v>
+        <v>9.043195446175018</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>9.033283735279824</v>
+        <v>9.034770756659746</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>9.039233043845268</v>
+        <v>9.040462873132974</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>9.038898247840432</v>
+        <v>9.039597700572227</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>9.048127859470604</v>
+        <v>9.047373857476286</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>9.056576110055897</v>
+        <v>9.053630737189643</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>9.010716714808527</v>
+        <v>9.0083501618876</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>8.981887294035907</v>
+        <v>8.980451845830537</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>8.964614077999009</v>
+        <v>8.965233567159018</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.748656337326924</v>
+        <v>9.748663113433118</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.723815033240474</v>
+        <v>9.723829932305939</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.720769276401551</v>
+        <v>9.720789820893964</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.700056250742097</v>
+        <v>9.700088942906671</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.704570579236128</v>
+        <v>9.704602937650527</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.697819962551257</v>
+        <v>9.697851914515017</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.693643303562521</v>
+        <v>9.693675411388737</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.707695503899721</v>
+        <v>9.707728413443119</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.720235697862661</v>
+        <v>9.720274247632361</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.72706661652882</v>
+        <v>9.727096367747869</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.735719022339758</v>
+        <v>9.73574914031304</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.712110110899838</v>
+        <v>9.712139604308268</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.6677238652033</v>
+        <v>9.667753448580392</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.633575961491122</v>
+        <v>9.633612882870748</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.600419330584661</v>
+        <v>9.600444007932497</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.56257501319898</v>
+        <v>9.562596558245207</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.504598232131009</v>
+        <v>9.504645148240764</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.432972068743497</v>
+        <v>9.433037447819592</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.357085079016883</v>
+        <v>9.3571461458572</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.289614612330713</v>
+        <v>9.289678658131564</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.266815656089687</v>
+        <v>9.266859843210337</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.279528976377488</v>
+        <v>9.279562721809162</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.23912178117893</v>
+        <v>9.239092789298036</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.170022737178169</v>
+        <v>9.169961951113567</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.105702860210542</v>
+        <v>9.105609156761759</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.011264334752255</v>
+        <v>9.01115162368443</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.940334480392044</v>
+        <v>8.940195877445554</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.937082372069499</v>
+        <v>8.936910083837383</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.946580644629858</v>
+        <v>8.946381190326099</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.070883105083729</v>
+        <v>9.070604397321688</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.124621674768374</v>
+        <v>9.12433030376817</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.29091706355322</v>
+        <v>9.290687678142671</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.384306130875279</v>
+        <v>9.384126474046777</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.403550556426264</v>
+        <v>9.403398631703611</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.487431202467683</v>
+        <v>9.48730093493471</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.607749027544173</v>
+        <v>9.607786818311052</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.59952304248195</v>
+        <v>9.59961991512586</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.617881939954565</v>
+        <v>9.618080197969416</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.616792710411664</v>
+        <v>9.617123839640795</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.598367696066568</v>
+        <v>9.598747843163077</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.63416990820123</v>
+        <v>9.634597827379736</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.501279109809829</v>
+        <v>9.501659218235178</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.433089459161305</v>
+        <v>9.433451966454211</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.284346447041795</v>
+        <v>9.284550423870698</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.187275800661515</v>
+        <v>9.187405267699077</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.076225814168012</v>
+        <v>9.076187486068914</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.048766888880666</v>
+        <v>9.048678796821784</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.045993976607443</v>
+        <v>9.04592346885244</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.020286119970132</v>
+        <v>9.020178484120102</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>8.99996295840274</v>
+        <v>8.999853249208508</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.011836917508795</v>
+        <v>9.011783162200999</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.039479002763736</v>
+        <v>9.039498481753467</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.059332758611298</v>
+        <v>9.059392565025039</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.060778687783095</v>
+        <v>9.060780828481406</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.04768623382787</v>
+        <v>9.047674511131071</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.038624083831273</v>
+        <v>9.038588680590202</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.046244375124591</v>
+        <v>9.046163509490956</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.061900019214701</v>
+        <v>9.06177676460187</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.073775888838824</v>
+        <v>9.073587615602136</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.088454909174645</v>
+        <v>9.08830742256621</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.072485612049242</v>
+        <v>9.072355022089436</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>9.057782251417041</v>
+        <v>9.05797693985425</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>9.0476285998951</v>
+        <v>9.047993716357597</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>9.048564808582491</v>
+        <v>9.048945016133406</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>9.048243936928319</v>
+        <v>9.048572402362087</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>9.043275352223763</v>
+        <v>9.043691936623681</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>9.043195446175018</v>
+        <v>9.04364358046241</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>9.034770756659746</v>
+        <v>9.03549670567662</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>9.040462873132974</v>
+        <v>9.040836267118838</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>9.039597700572227</v>
+        <v>9.039364730070023</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>9.047373857476286</v>
+        <v>9.045579838985116</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>9.053630737189643</v>
+        <v>9.049584610700609</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>9.0083501618876</v>
+        <v>9.004449356305157</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>8.980451845830537</v>
+        <v>8.976536229026623</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>8.965233567159018</v>
+        <v>8.958240159043825</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.748663113433118</v>
+        <v>9.748669752662391</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.723829932305939</v>
+        <v>9.723844530597336</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.720789820893964</v>
+        <v>9.720809951374026</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.700088942906671</v>
+        <v>9.700120975396359</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.704602937650527</v>
+        <v>9.704634643000645</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.697851914515017</v>
+        <v>9.697883221567499</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.693675411388737</v>
+        <v>9.693706870774635</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.707728413443119</v>
+        <v>9.707760657434589</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.720274247632361</v>
+        <v>9.720312020242657</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.727096367747869</v>
+        <v>9.727125520085801</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.73574914031304</v>
+        <v>9.735778652025338</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.712139604308268</v>
+        <v>9.712168504139211</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.667753448580392</v>
+        <v>9.667782439876405</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.633612882870748</v>
+        <v>9.633649065432211</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.600444007932497</v>
+        <v>9.600468193436612</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.562596558245207</v>
+        <v>9.562617670155809</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.504645148240764</v>
+        <v>9.504691117823407</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.433037447819592</v>
+        <v>9.433101514893689</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.3571461458572</v>
+        <v>9.357205985738005</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.289678658131564</v>
+        <v>9.289741422687452</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.266859843210337</v>
+        <v>9.266903180036211</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.279562721809162</v>
+        <v>9.279595843208606</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.239092789298036</v>
+        <v>9.239064428036901</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.169961951113567</v>
+        <v>9.169902445953765</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.105609156761759</v>
+        <v>9.105517409553439</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.01115162368443</v>
+        <v>9.011041259174645</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.940195877445554</v>
+        <v>8.940060151282871</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.936910083837383</v>
+        <v>8.93674135417951</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.946381190326099</v>
+        <v>8.94618577764644</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.070604397321688</v>
+        <v>9.07033129462793</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.12433030376817</v>
+        <v>9.124044790481021</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.290687678142671</v>
+        <v>9.29046281964019</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.384126474046777</v>
+        <v>9.38395033646437</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.403398631703611</v>
+        <v>9.403249618965281</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.48730093493471</v>
+        <v>9.487173101585103</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.607786818311052</v>
+        <v>9.607823673111049</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.59961991512586</v>
+        <v>9.599714625616652</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.618080197969416</v>
+        <v>9.618274283642304</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.617123839640795</v>
+        <v>9.617448247204036</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.598747843163077</v>
+        <v>9.599120316457418</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.634597827379736</v>
+        <v>9.63501716700007</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.501659218235178</v>
+        <v>9.502031849653566</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.433451966454211</v>
+        <v>9.433807420291561</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.284550423870698</v>
+        <v>9.284750515566067</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.187405267699077</v>
+        <v>9.187532320942021</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.076187486068914</v>
+        <v>9.076149980433858</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.048678796821784</v>
+        <v>9.04859244820743</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.04592346885244</v>
+        <v>9.045854342736865</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.020178484120102</v>
+        <v>9.02007290373983</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>8.999853249208508</v>
+        <v>8.999745584602934</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.011783162200999</v>
+        <v>9.011730353620594</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.039498481753467</v>
+        <v>9.039517512850558</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.059392565025039</v>
+        <v>9.059451214348904</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.060780828481406</v>
+        <v>9.060783055538963</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.047674511131071</v>
+        <v>9.047663078813251</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.038588680590202</v>
+        <v>9.038553993328549</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.046163509490956</v>
+        <v>9.046084180607785</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.06177676460187</v>
+        <v>9.061655766725305</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.073587615602136</v>
+        <v>9.073402736322247</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.08830742256621</v>
+        <v>9.088162675387254</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.072355022089436</v>
+        <v>9.072226690031027</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>9.05797693985425</v>
+        <v>9.058073081651496</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>9.047993716357597</v>
+        <v>9.048225194626006</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>9.048945016133406</v>
+        <v>9.049142535340152</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>9.048572402362087</v>
+        <v>9.048664450283663</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>9.043691936623681</v>
+        <v>9.043775555830763</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>9.04364358046241</v>
+        <v>9.043707752861083</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>9.03549670567662</v>
+        <v>9.035775682006852</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>9.040836267118838</v>
+        <v>9.040757123982141</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>9.039364730070023</v>
+        <v>9.038752440661481</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>9.045579838985116</v>
+        <v>9.043513361146751</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>9.049584610700609</v>
+        <v>9.045480761109605</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>9.004449356305157</v>
+        <v>9.000487126105094</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>8.976536229026623</v>
+        <v>8.972498162203809</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>8.958240159043825</v>
+        <v>8.95211339096258</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.748669752662391</v>
+        <v>9.748676259120488</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.723844530597336</v>
+        <v>9.723858837130841</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.720809951374026</v>
+        <v>9.720829680230164</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.700120975396359</v>
+        <v>9.700152367975209</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.704634643000645</v>
+        <v>9.704665714856134</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.697883221567499</v>
+        <v>9.697913903035516</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.693706870774635</v>
+        <v>9.693737701164149</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.707760657434589</v>
+        <v>9.707792255858505</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.720312020242657</v>
+        <v>9.720349038953442</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.727125520085801</v>
+        <v>9.727154091441395</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.735778652025338</v>
+        <v>9.735807575595878</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.712168504139211</v>
+        <v>9.712196828129533</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.667782439876405</v>
+        <v>9.667810856683722</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.633649065432211</v>
+        <v>9.633684531123155</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.600468193436612</v>
+        <v>9.600491901649551</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.562617670155809</v>
+        <v>9.56263836185861</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.504691117823407</v>
+        <v>9.504736169225236</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.433101514893689</v>
+        <v>9.433164309040356</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.357205985738005</v>
+        <v>9.357264635247951</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.289741422687452</v>
+        <v>9.289802944046258</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.266903180036211</v>
+        <v>9.266945690804196</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.279595843208606</v>
+        <v>9.279628357576163</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.239064428036901</v>
+        <v>9.239036677169175</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.169902445953765</v>
+        <v>9.169844181755085</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.105517409553439</v>
+        <v>9.105427558106722</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.011041259174645</v>
+        <v>9.010933168878179</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.940060151282871</v>
+        <v>8.939927213479661</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.93674135417951</v>
+        <v>8.936576074237845</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.94618577764644</v>
+        <v>8.945994285133153</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.07033129462793</v>
+        <v>9.070063629829288</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.124044790481021</v>
+        <v>9.123764960261255</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.29046281964019</v>
+        <v>9.290242355609301</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.38395033646437</v>
+        <v>9.383777615988357</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.403249618965281</v>
+        <v>9.403103435682734</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.487173101585103</v>
+        <v>9.487047635408301</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.607823673111049</v>
+        <v>9.607859625082057</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.599714625616652</v>
+        <v>9.599807244749694</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.618274283642304</v>
+        <v>9.618464326809764</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.617448247204036</v>
+        <v>9.617766135361208</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.599120316457418</v>
+        <v>9.599485345522842</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.63501716700007</v>
+        <v>9.635428182099236</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.502031849653566</v>
+        <v>9.502397222087243</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.433807420291561</v>
+        <v>9.43415602397252</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.284750515566067</v>
+        <v>9.284946831558663</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.187532320942021</v>
+        <v>9.187657026844136</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.076149980433858</v>
+        <v>9.076113271309488</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.04859244820743</v>
+        <v>9.048507791968481</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.045854342736865</v>
+        <v>9.045786558230461</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.02007290373983</v>
+        <v>9.01996932079061</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>8.999745584602934</v>
+        <v>8.999639908352666</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.011730353620594</v>
+        <v>9.011678467422414</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.039517512850558</v>
+        <v>9.039536111008015</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.059451214348904</v>
+        <v>9.059508739682578</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.060783055538963</v>
+        <v>9.060785362620608</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.047663078813251</v>
+        <v>9.047651926904271</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.038553993328549</v>
+        <v>9.038520000897945</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.046084180607785</v>
+        <v>9.046006345630811</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.061655766725305</v>
+        <v>9.061536965107535</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.073402736322247</v>
+        <v>9.07322116151154</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.088162675387254</v>
+        <v>9.08802059333722</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.072226690031027</v>
+        <v>9.07210056038968</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>9.058073081651496</v>
+        <v>9.058168774165981</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>9.048225194626006</v>
+        <v>9.048462811582482</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>9.049142535340152</v>
+        <v>9.049366023919792</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>9.048664450283663</v>
+        <v>9.048803263520611</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>9.043775555830763</v>
+        <v>9.043900112603382</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>9.043707752861083</v>
+        <v>9.043812884754836</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>9.035775682006852</v>
+        <v>9.036088818952482</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>9.040757123982141</v>
+        <v>9.040733157047786</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>9.038752440661481</v>
+        <v>9.038224071060334</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>9.043513361146751</v>
+        <v>9.04163946181226</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>9.045480761109605</v>
+        <v>9.041761056434371</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>9.000487126105094</v>
+        <v>8.996985184231807</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>8.972498162203809</v>
+        <v>8.969132479418782</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>8.95211339096258</v>
+        <v>8.948142393123067</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B116"/>
+  <dimension ref="A1:B117"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.748676259120488</v>
+        <v>9.748682636750589</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.723858837130841</v>
+        <v>9.723872860565844</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.720829680230164</v>
+        <v>9.720849019361474</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.700152367975209</v>
+        <v>9.700183139625683</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.704665714856134</v>
+        <v>9.704696172012616</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.697913903035516</v>
+        <v>9.697943977481392</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.693737701164149</v>
+        <v>9.693767921231649</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.707792255858505</v>
+        <v>9.707823227907209</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.720349038953442</v>
+        <v>9.720385326105806</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.727154091441395</v>
+        <v>9.727182099007367</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.735807575595878</v>
+        <v>9.735835928429138</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.712196828129533</v>
+        <v>9.712224593316556</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.667810856683722</v>
+        <v>9.667838715904848</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.633684531123155</v>
+        <v>9.633719301030792</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.600491901649551</v>
+        <v>9.600515146555637</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.56263836185861</v>
+        <v>9.562658645772173</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.504736169225236</v>
+        <v>9.504780329672325</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.433164309040356</v>
+        <v>9.433225867798789</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.357264635247951</v>
+        <v>9.357322129536071</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.289802944046258</v>
+        <v>9.289863258764877</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.266945690804196</v>
+        <v>9.266987398841666</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.279628357576163</v>
+        <v>9.279660281306578</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.239036677169175</v>
+        <v>9.239009517319763</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.169844181755085</v>
+        <v>9.169787120213053</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.105427558106722</v>
+        <v>9.105339544404746</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.010933168878179</v>
+        <v>9.010827283387131</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.939927213479661</v>
+        <v>8.939796979190445</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.936576074237845</v>
+        <v>8.936414139539405</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.945994285133153</v>
+        <v>8.945806596140908</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.070063629829288</v>
+        <v>9.069801242326299</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.123764960261255</v>
+        <v>9.123490645328173</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.290242355609301</v>
+        <v>9.290026158719314</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.383777615988357</v>
+        <v>9.383608214383209</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.403103435682734</v>
+        <v>9.402960002400576</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.487047635408301</v>
+        <v>9.486924471806567</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.607859625082057</v>
+        <v>9.607894705854086</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.599807244749694</v>
+        <v>9.599897840290797</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.618464326809764</v>
+        <v>9.61865045199524</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.617766135361208</v>
+        <v>9.618077698351374</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.599485345522842</v>
+        <v>9.599843150883647</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.635428182099236</v>
+        <v>9.635831117721633</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.502397222087243</v>
+        <v>9.502755545181255</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.43415602397252</v>
+        <v>9.434497973080854</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.284946831558663</v>
+        <v>9.285139477228871</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.187657026844136</v>
+        <v>9.187779449459303</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.076113271309488</v>
+        <v>9.07607733381456</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.048507791968481</v>
+        <v>9.048424779004002</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.045786558230461</v>
+        <v>9.045720076827177</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.01996932079061</v>
+        <v>9.019867679387044</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>8.999639908352666</v>
+        <v>8.999536166251666</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.011678467422414</v>
+        <v>9.0116274800698</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.039536111008015</v>
+        <v>9.039554290531111</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.059508739682578</v>
+        <v>9.059565172881577</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.060785362620608</v>
+        <v>9.060787743784154</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.047651926904271</v>
+        <v>9.047641045865248</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.038520000897945</v>
+        <v>9.038486682961656</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.046006345630811</v>
+        <v>9.045929963272346</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.061536965107535</v>
+        <v>9.061420301375966</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.07322116151154</v>
+        <v>9.073042804744222</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.08802059333722</v>
+        <v>9.087881104725557</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.07210056038968</v>
+        <v>9.071976579372826</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>9.058168774165981</v>
+        <v>9.058024404320021</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>9.048462811582482</v>
+        <v>9.048423153882602</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>9.049366023919792</v>
+        <v>9.049053355730507</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>9.048803263520611</v>
+        <v>9.048449946758979</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>9.043900112603382</v>
+        <v>9.04320050567024</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>9.043812884754836</v>
+        <v>9.043415869966115</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>9.036088818952482</v>
+        <v>9.035838321553017</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>9.040733157047786</v>
+        <v>9.040020922299163</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>9.038224071060334</v>
+        <v>9.036793445594544</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>9.04163946181226</v>
+        <v>9.038749316502983</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>9.041761056434371</v>
+        <v>9.036589531468321</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>8.996985184231807</v>
+        <v>8.991532298444799</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>8.969132479418782</v>
+        <v>8.963148071706561</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,15 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>8.948142393123067</v>
+        <v>8.939959019073049</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117" s="3">
+        <v>46374</v>
+      </c>
+      <c r="B117">
+        <v>8.888406927606262</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.748682636750589</v>
+        <v>9.748688889341256</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.723872860565844</v>
+        <v>9.723886609222445</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.720849019361474</v>
+        <v>9.72086798020166</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.700183139625683</v>
+        <v>9.700213308586921</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.704696172012616</v>
+        <v>9.704726032529567</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.697943977481392</v>
+        <v>9.697973462740382</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.693767921231649</v>
+        <v>9.693797548919633</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.707823227907209</v>
+        <v>9.70785359201987</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.720385326105806</v>
+        <v>9.720420903167003</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.727182099007367</v>
+        <v>9.727209559304834</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.735835928429138</v>
+        <v>9.735863727249731</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.712224593316556</v>
+        <v>9.712251816072202</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.667838715904848</v>
+        <v>9.667866033785891</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.633719301030792</v>
+        <v>9.63375339542362</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.600515146555637</v>
+        <v>9.600537941598414</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.562658645772173</v>
+        <v>9.562678533830605</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.504780329672325</v>
+        <v>9.504823625325288</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.433225867798789</v>
+        <v>9.433286227247446</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.357322129536071</v>
+        <v>9.357378502381849</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.289863258764877</v>
+        <v>9.28992240198148</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.266987398841666</v>
+        <v>9.267028326608584</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.279660281306578</v>
+        <v>9.279691630215384</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.239009517319763</v>
+        <v>9.238982929920686</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.169787120213053</v>
+        <v>9.169731224579371</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.105339544404746</v>
+        <v>9.105253312768896</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.010827283387131</v>
+        <v>9.010723536083219</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.939796979190445</v>
+        <v>8.93966936696974</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.936414139539405</v>
+        <v>8.936255449778159</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.945806596140908</v>
+        <v>8.945622598601064</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.069801242326299</v>
+        <v>9.069543977773645</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.123490645328173</v>
+        <v>9.12322168443246</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.290026158719314</v>
+        <v>9.289814106502121</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.383608214383209</v>
+        <v>9.383442037133339</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.402960002400576</v>
+        <v>9.402819242595694</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.486924471806567</v>
+        <v>9.486803548488645</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.607894705854086</v>
+        <v>9.607928945632551</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.599897840290797</v>
+        <v>9.59998647713534</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.61865045199524</v>
+        <v>9.618832778677247</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.618077698351374</v>
+        <v>9.618383122785886</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.599843150883647</v>
+        <v>9.6001939444558</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.635831117721633</v>
+        <v>9.636226209402949</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.502755545181255</v>
+        <v>9.503107020601098</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.434497973080854</v>
+        <v>9.434833455846382</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.285139477228871</v>
+        <v>9.28532855409135</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.187779449459303</v>
+        <v>9.187899650548005</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.07607733381456</v>
+        <v>9.076042144085534</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.048424779004002</v>
+        <v>9.048343362087671</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.045720076827177</v>
+        <v>9.045654861473688</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.019867679387044</v>
+        <v>9.019767925698689</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>8.999536166251666</v>
+        <v>8.999434306031493</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.0116274800698</v>
+        <v>9.011577368802339</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.039554290531111</v>
+        <v>9.039572065111637</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.059565172881577</v>
+        <v>9.059620544614853</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.060787743784154</v>
+        <v>9.060790193454482</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.047641045865248</v>
+        <v>9.047630426566274</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.038486682961656</v>
+        <v>9.038454019956603</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.045929963272346</v>
+        <v>9.045854993732284</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.061420301375966</v>
+        <v>9.061305719173921</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.073042804744222</v>
+        <v>9.07286758252924</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.087881104725557</v>
+        <v>9.087744140360762</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.071976579372826</v>
+        <v>9.071854694821871</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>9.058024404320021</v>
+        <v>9.057882347148936</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>9.048423153882602</v>
+        <v>9.048093870916372</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>9.049053355730507</v>
+        <v>9.048386159527487</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>9.048449946758979</v>
+        <v>9.047461492408074</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>9.04320050567024</v>
+        <v>9.042036403325534</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>9.043415869966115</v>
+        <v>9.042482328859954</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>9.035838321553017</v>
+        <v>9.034962570526028</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>9.040020922299163</v>
+        <v>9.03861507567251</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>9.036793445594544</v>
+        <v>9.034640031629124</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>9.038749316502983</v>
+        <v>9.035135273894301</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>9.036589531468321</v>
+        <v>9.030730470093149</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>8.991532298444799</v>
+        <v>8.98526495544645</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>8.963148071706561</v>
+        <v>8.956075049065818</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>8.939959019073049</v>
+        <v>8.930182383763864</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>8.888406927606262</v>
+        <v>8.873312662954074</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>9.048093870916372</v>
+        <v>9.046422929227042</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>9.048386159527487</v>
+        <v>9.046335502404748</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>9.047461492408074</v>
+        <v>9.045423952222844</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>9.042036403325534</v>
+        <v>9.04035036205498</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>9.042482328859954</v>
+        <v>9.039860422177199</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>9.034962570526028</v>
+        <v>9.032019859151649</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>9.03861507567251</v>
+        <v>9.035240964261064</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>9.034640031629124</v>
+        <v>9.030828902835742</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>9.035135273894301</v>
+        <v>9.03061530769949</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>9.030730470093149</v>
+        <v>9.025045848210848</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>8.98526495544645</v>
+        <v>8.977994314277986</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>8.956075049065818</v>
+        <v>8.94598670921793</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>8.930182383763864</v>
+        <v>8.91165392114176</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>8.873312662954074</v>
+        <v>8.800009129594706</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.748688889341256</v>
+        <v>9.748695020533955</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.723886609222445</v>
+        <v>9.723900091097882</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.72086798020166</v>
+        <v>9.720886573741545</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.700213308586921</v>
+        <v>9.700242892390756</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.704726032529567</v>
+        <v>9.704755313765999</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.697973462740382</v>
+        <v>9.698002375955928</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.693797548919633</v>
+        <v>9.69382660147423</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.70785359201987</v>
+        <v>9.707883365919047</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.720420903167003</v>
+        <v>9.720455790772714</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.727209559304834</v>
+        <v>9.72723648821578</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.735863727249731</v>
+        <v>9.735890988135267</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.712251816072202</v>
+        <v>9.712278512135153</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.667866033785891</v>
+        <v>9.667892825948105</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.63375339542362</v>
+        <v>9.633786833790772</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.600537941598414</v>
+        <v>9.600560299706519</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.562678533830605</v>
+        <v>9.562698037506973</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.504823625325288</v>
+        <v>9.504866081330878</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.433286227247446</v>
+        <v>9.433345422074357</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.357378502381849</v>
+        <v>9.357433786261232</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.28992240198148</v>
+        <v>9.289980407483661</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.267028326608584</v>
+        <v>9.26706849573733</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.279691630215384</v>
+        <v>9.279722419563949</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.238982929920686</v>
+        <v>9.238956897169704</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.169731224579371</v>
+        <v>9.169676459583885</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.105253312768896</v>
+        <v>9.105168809742423</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.010723536083219</v>
+        <v>9.010621862999317</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.93966936696974</v>
+        <v>8.939544298603792</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.936255449778159</v>
+        <v>8.936099908609748</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.945622598601064</v>
+        <v>8.945442184799639</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.069543977773645</v>
+        <v>9.069291687779035</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.12322168443246</v>
+        <v>9.122957922541861</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.289814106502121</v>
+        <v>9.289606081122731</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.383442037133339</v>
+        <v>9.383278993269128</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.402819242595694</v>
+        <v>9.402681082543921</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.486803548488645</v>
+        <v>9.486684805368887</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.607928945632551</v>
+        <v>9.607962373276097</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.59998647713534</v>
+        <v>9.600073217457528</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.618832778677247</v>
+        <v>9.619011421541483</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.618383122785886</v>
+        <v>9.618682588018538</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.6001939444558</v>
+        <v>9.600537929962115</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.636226209402949</v>
+        <v>9.63661368362617</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.503107020601098</v>
+        <v>9.503451842407998</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.434833455846382</v>
+        <v>9.43516265348633</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.28532855409135</v>
+        <v>9.285514159969686</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.187899650548005</v>
+        <v>9.188017689678265</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.076042144085534</v>
+        <v>9.07600767922542</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.048343362087671</v>
+        <v>9.048263495779477</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.045654861473688</v>
+        <v>9.045590876501853</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.019767925698689</v>
+        <v>9.019670007856973</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>8.999434306031493</v>
+        <v>8.999334277276237</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.011577368802339</v>
+        <v>9.011528111605084</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.039572065111637</v>
+        <v>9.039589447860038</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.059620544614853</v>
+        <v>9.059674884419232</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.060790193454482</v>
+        <v>9.060792706399514</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.047630426566274</v>
+        <v>9.047620060265466</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.038454019956603</v>
+        <v>9.03842199305752</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.045854993732284</v>
+        <v>9.045781398632657</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.061305719173921</v>
+        <v>9.061193164076037</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.07286758252924</v>
+        <v>9.072695414189283</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.087744140360762</v>
+        <v>9.087609633444885</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.071854694821871</v>
+        <v>9.07173485615635</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>9.057882347148936</v>
+        <v>9.057742551020807</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>9.046422929227042</v>
+        <v>9.04372387477966</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>9.046335502404748</v>
+        <v>9.042771981276442</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>9.045423952222844</v>
+        <v>9.04150973682999</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>9.04035036205498</v>
+        <v>9.036496823089184</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>9.039860422177199</v>
+        <v>9.03526964116411</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>9.032019859151649</v>
+        <v>9.027064618221704</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>9.035240964261064</v>
+        <v>9.029214105398228</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>9.030828902835742</v>
+        <v>9.02351848700078</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>9.03061530769949</v>
+        <v>9.021018970916781</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>9.025045848210848</v>
+        <v>9.011909716331292</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>8.977994314277986</v>
+        <v>8.962600661023483</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>8.94598670921793</v>
+        <v>8.926731347733735</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>8.91165392114176</v>
+        <v>8.882168266340681</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>8.800009129594706</v>
+        <v>8.748073107771695</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.748695020533955</v>
+        <v>9.748701033830109</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.723900091097882</v>
+        <v>9.72391331388207</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.720886573741545</v>
+        <v>9.720904810550323</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.700242892390756</v>
+        <v>9.700271907895665</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.704755313765999</v>
+        <v>9.704784032414077</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.698002375955928</v>
+        <v>9.698030733612867</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.69382660147423</v>
+        <v>9.693855095478643</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.707883365919047</v>
+        <v>9.707912566645174</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.720455790772714</v>
+        <v>9.720490008766919</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.72723648821578</v>
+        <v>9.72726290101367</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.735890988135267</v>
+        <v>9.73591772654734</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.712278512135153</v>
+        <v>9.712304696641166</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.667892825948105</v>
+        <v>9.667919107417635</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.633786833790772</v>
+        <v>9.633819634879107</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.600560299706519</v>
+        <v>9.600582233318093</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.562698037506973</v>
+        <v>9.562717167835332</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.504866081330878</v>
+        <v>9.504907721870616</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.433345422074357</v>
+        <v>9.433403485643446</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.357433786261232</v>
+        <v>9.35748801240889</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.289980407483661</v>
+        <v>9.29003730777268</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.26706849573733</v>
+        <v>9.267107927070334</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.279722419563949</v>
+        <v>9.279752664083267</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.238956897169704</v>
+        <v>9.238931401991405</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.169676459583885</v>
+        <v>9.169622791361173</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.105168809742423</v>
+        <v>9.105085983980924</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.010621862999317</v>
+        <v>9.010522202689135</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.939544298603792</v>
+        <v>8.939421698952202</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.936099908609748</v>
+        <v>8.935947423458227</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.945442184799639</v>
+        <v>8.945265251168092</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.069291687779035</v>
+        <v>9.069044229619324</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.122957922541861</v>
+        <v>9.122699210544791</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.289606081122731</v>
+        <v>9.289401969162661</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.383278993269128</v>
+        <v>9.383118995202633</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.402681082543921</v>
+        <v>9.402545451193982</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.486684805368887</v>
+        <v>9.486568184471572</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.607962373276097</v>
+        <v>9.607995016369513</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.600073217457528</v>
+        <v>9.600158120850477</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.619011421541483</v>
+        <v>9.619186490718059</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.618682588018538</v>
+        <v>9.618976266494482</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.600537929962115</v>
+        <v>9.600875303323694</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.63661368362617</v>
+        <v>9.636993758251702</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.503451842407998</v>
+        <v>9.503790197413249</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.43516265348633</v>
+        <v>9.435485740527923</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.285514159969686</v>
+        <v>9.285696389161732</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.188017689678265</v>
+        <v>9.188133624321306</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.07600767922542</v>
+        <v>9.075973917255643</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.048263495779477</v>
+        <v>9.048185136342358</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.045590876501853</v>
+        <v>9.04552808756489</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.019670007856973</v>
+        <v>9.019573875867117</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>8.999334277276237</v>
+        <v>8.999236031341887</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.011528111605084</v>
+        <v>9.011479687179149</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.039589447860038</v>
+        <v>9.039606451335555</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.059674884419232</v>
+        <v>9.0597282207509</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.060792706399514</v>
+        <v>9.060795277707918</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.047620060265466</v>
+        <v>9.047609938589236</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.03842199305752</v>
+        <v>9.038390584143009</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.045781398632657</v>
+        <v>9.045709140955573</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.061193164076037</v>
+        <v>9.061082583507785</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.072695414189283</v>
+        <v>9.072526221745598</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.087609633444885</v>
+        <v>9.087477519473179</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.07173485615635</v>
+        <v>9.071617014319965</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>9.057742551020807</v>
+        <v>9.057604965679198</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>9.04372387477966</v>
+        <v>9.041493766220498</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>9.042771981276442</v>
+        <v>9.039775097954102</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>9.04150973682999</v>
+        <v>9.038199970279724</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>9.036496823089184</v>
+        <v>9.03337486021938</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>9.03526964116411</v>
+        <v>9.031361084437071</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>9.027064618221704</v>
+        <v>9.022871551850983</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>9.029214105398228</v>
+        <v>9.024097511494404</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>9.02351848700078</v>
+        <v>9.017286547397898</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>9.021018970916781</v>
+        <v>9.01280936591286</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>9.011909716331292</v>
+        <v>9.000669174800912</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>8.962600661023483</v>
+        <v>8.949736951186829</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>8.926731347733735</v>
+        <v>8.911283766677688</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>8.882168266340681</v>
+        <v>8.86110289795219</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>8.748073107771695</v>
+        <v>8.728383875159796</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.748701033830109</v>
+        <v>9.748706932597777</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.72391331388207</v>
+        <v>9.723926284972194</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.720904810550323</v>
+        <v>9.720922700795569</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.700271907895665</v>
+        <v>9.700300371318793</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.704784032414077</v>
+        <v>9.70481220453086</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.698030733612867</v>
+        <v>9.69805855156876</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.693855095478643</v>
+        <v>9.693883046884707</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.707912566645174</v>
+        <v>9.707941210589059</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.720490008766919</v>
+        <v>9.720523576239509</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.72726290101367</v>
+        <v>9.727288812392301</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.73591772654734</v>
+        <v>9.735943957360753</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.712304696641166</v>
+        <v>9.71233038415167</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.667919107417635</v>
+        <v>9.667944892653587</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.633819634879107</v>
+        <v>9.633851816728191</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.600582233318093</v>
+        <v>9.600603754403833</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.562717167835332</v>
+        <v>9.562735935431526</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.504907721870616</v>
+        <v>9.504948570206636</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.433403485643446</v>
+        <v>9.43346045005705</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.35748801240889</v>
+        <v>9.357541210876917</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.29003730777268</v>
+        <v>9.290093134124064</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.267107927070334</v>
+        <v>9.267146640695691</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.279752664083267</v>
+        <v>9.279782377996522</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.238931401991405</v>
+        <v>9.238906428000657</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.169622791361173</v>
+        <v>9.169570187381467</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.105085983980924</v>
+        <v>9.105004786149241</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.010522202689135</v>
+        <v>9.010424496104513</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.939421698952202</v>
+        <v>8.939301495798736</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.935947423458227</v>
+        <v>8.935797905333979</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.945265251168092</v>
+        <v>8.94509169808601</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.069044229619324</v>
+        <v>9.068801465972667</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.122699210544791</v>
+        <v>9.12244540497073</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.289401969162661</v>
+        <v>9.289201661415337</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.383118995202633</v>
+        <v>9.382961958572299</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.402545451193982</v>
+        <v>9.402412280048061</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.486568184471572</v>
+        <v>9.486453629840103</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.607995016369513</v>
+        <v>9.608026901291993</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.600158120850477</v>
+        <v>9.600241244457814</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.619186490718059</v>
+        <v>9.619358092004751</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.618976266494482</v>
+        <v>9.619264324079158</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.600875303323694</v>
+        <v>9.601206253029165</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.636993758251702</v>
+        <v>9.637366642923205</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.503790197413249</v>
+        <v>9.504122265512956</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.435485740527923</v>
+        <v>9.435802885113372</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.285696389161732</v>
+        <v>9.285875332596209</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.188133624321306</v>
+        <v>9.188247509942357</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.075973917255643</v>
+        <v>9.075940837070766</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.048185136342358</v>
+        <v>9.048108241663435</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.04552808756489</v>
+        <v>9.045466461577048</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.019573875867117</v>
+        <v>9.019479481524709</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>8.999236031341887</v>
+        <v>8.999139521279782</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.011479687179149</v>
+        <v>9.011432074913627</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.039606451335555</v>
+        <v>9.039623087574537</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.0597282207509</v>
+        <v>9.059780581034136</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.060795277707918</v>
+        <v>9.060797902768389</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.047609938589236</v>
+        <v>9.047600053513751</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.038390584143009</v>
+        <v>9.038359775763446</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.045709140955573</v>
+        <v>9.045638184984314</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.061082583507785</v>
+        <v>9.06097392666889</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.072526221745598</v>
+        <v>9.072359929808286</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.087477519473179</v>
+        <v>9.08734773613862</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.071617014319965</v>
+        <v>9.071501121728424</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>9.057604965679198</v>
+        <v>9.057469542206139</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>9.041493766220498</v>
+        <v>9.039363689230674</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>9.039775097954102</v>
+        <v>9.036895080284289</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>9.038199970279724</v>
+        <v>9.035036412861572</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>9.03337486021938</v>
+        <v>9.029818390629915</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>9.031361084437071</v>
+        <v>9.027626780526642</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>9.022871551850983</v>
+        <v>9.018877720298336</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>9.024097511494404</v>
+        <v>9.019242993789105</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>9.017286547397898</v>
+        <v>9.011394541641952</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>9.01280936591286</v>
+        <v>9.005102727500187</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>9.000669174800912</v>
+        <v>8.990231232504293</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>8.949736951186829</v>
+        <v>8.937990964536301</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>8.911283766677688</v>
+        <v>8.897586219451281</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>8.86110289795219</v>
+        <v>8.843874792572656</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>8.728383875159796</v>
+        <v>8.716507327449378</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B117"/>
+  <dimension ref="A1:B118"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.748706932597777</v>
+        <v>9.748712720077943</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.723926284972194</v>
+        <v>9.723939011486531</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.720922700795569</v>
+        <v>9.720940254262143</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.700300371318793</v>
+        <v>9.700328298266147</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.70481220453086</v>
+        <v>9.704839845568186</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.69805855156876</v>
+        <v>9.698085845083433</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.693883046884707</v>
+        <v>9.69391047104264</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.707941210589059</v>
+        <v>9.70796931352254</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.720523576239509</v>
+        <v>9.720556511561739</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.727288812392301</v>
+        <v>9.727314236493044</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.735943957360753</v>
+        <v>9.735969694891072</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.71233038415167</v>
+        <v>9.712355588680744</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.667944892653587</v>
+        <v>9.667970195574501</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.633851816728191</v>
+        <v>9.633883396703347</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.600603754403833</v>
+        <v>9.600624874488703</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.562735935431526</v>
+        <v>9.562754350512803</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.504948570206636</v>
+        <v>9.504988648724957</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.43346045005705</v>
+        <v>9.433516346214972</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.357541210876917</v>
+        <v>9.357593410590235</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.290093134124064</v>
+        <v>9.290147916644823</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.267146640695691</v>
+        <v>9.26718465598087</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.279782377996522</v>
+        <v>9.279811575040549</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.238906428000657</v>
+        <v>9.238881959468229</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.169570187381467</v>
+        <v>9.169518616385611</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.105004786149241</v>
+        <v>9.104925168824311</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.010424496104513</v>
+        <v>9.010328686479788</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.939301495798736</v>
+        <v>8.939183619710727</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.935797905333979</v>
+        <v>8.935651268662065</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.94509169808601</v>
+        <v>8.944921429694979</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.068801465972667</v>
+        <v>9.068563264665713</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.12244540497073</v>
+        <v>9.122196367726293</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.289201661415337</v>
+        <v>9.289005052692739</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.382961958572299</v>
+        <v>9.382807802096133</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.402412280048061</v>
+        <v>9.402281503048723</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.486453629840103</v>
+        <v>9.486341087450779</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.608026901291993</v>
+        <v>9.608058053281127</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.600241244457814</v>
+        <v>9.600322643097343</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.619358092004751</v>
+        <v>9.619526327077363</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.619264324079158</v>
+        <v>9.619546920368681</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.601206253029165</v>
+        <v>9.60153096048318</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.637366642923205</v>
+        <v>9.63773253945077</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.504122265512956</v>
+        <v>9.504448220004463</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.435802885113372</v>
+        <v>9.436114249288407</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.285875332596209</v>
+        <v>9.286051077981057</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.188247509942357</v>
+        <v>9.188359400086746</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.075940837070766</v>
+        <v>9.075908418395832</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.048108241663435</v>
+        <v>9.048032771179551</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.045466461577048</v>
+        <v>9.045405966656514</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.019479481524709</v>
+        <v>9.019386778336695</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>8.999139521279782</v>
+        <v>8.999044701763999</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.011432074913627</v>
+        <v>9.01138525485878</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.039623087574537</v>
+        <v>9.03963936811704</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.059780581034136</v>
+        <v>9.059831991707417</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.060797902768389</v>
+        <v>9.060800577250422</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.047600053513751</v>
+        <v>9.047590397347426</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.038359775763446</v>
+        <v>9.038329551110598</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.045638184984314</v>
+        <v>9.045568496247434</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.06097392666889</v>
+        <v>9.060867144460458</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.072359929808286</v>
+        <v>9.072196465471766</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.08734773613862</v>
+        <v>9.087220223241044</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.071501121728424</v>
+        <v>9.071387132219124</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>9.057469542206139</v>
+        <v>9.057336232985655</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>9.039363689230674</v>
+        <v>9.039255401418346</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>9.036895080284289</v>
+        <v>9.034300181007442</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>9.035036412861572</v>
+        <v>9.031853506016166</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>9.029818390629915</v>
+        <v>9.026410712979501</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>9.027626780526642</v>
+        <v>9.023600227186929</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>9.018877720298336</v>
+        <v>9.014836217416075</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>9.019242993789105</v>
+        <v>9.014606536905067</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>9.011394541641952</v>
+        <v>9.005966929913972</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>9.005102727500187</v>
+        <v>8.998139949969975</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>8.990231232504293</v>
+        <v>8.981487753681346</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>8.937990964536301</v>
+        <v>8.927781981853547</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>8.897586219451281</v>
+        <v>8.886044354709714</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>8.843874792572656</v>
+        <v>8.830362153381607</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,15 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>8.716507327449378</v>
+        <v>8.709736273122314</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118" s="3">
+        <v>46381</v>
+      </c>
+      <c r="B118">
+        <v>8.653633893643274</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.748712720077943</v>
+        <v>9.748718399390448</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.723939011486531</v>
+        <v>9.723951500277449</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.720940254262143</v>
+        <v>9.720957480370014</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.700328298266147</v>
+        <v>9.700355703761121</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.704839845568186</v>
+        <v>9.704866970400939</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.698085845083433</v>
+        <v>9.698112628846886</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.69391047104264</v>
+        <v>9.693937382729134</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.70796931352254</v>
+        <v>9.707996890627424</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.720556511561739</v>
+        <v>9.720588832419743</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.727314236493044</v>
+        <v>9.727339186930559</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.735969694891072</v>
+        <v>9.735994952920674</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.712355588680744</v>
+        <v>9.712380323720588</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.667970195574501</v>
+        <v>9.667995029583386</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.633883396703347</v>
+        <v>9.633914391526831</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.600624874488703</v>
+        <v>9.600645604672501</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.562754350512803</v>
+        <v>9.562772422916353</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.504988648724957</v>
+        <v>9.505027978976331</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.433516346214972</v>
+        <v>9.433571203870232</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.357593410590235</v>
+        <v>9.357644639398941</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.290147916644823</v>
+        <v>9.29020168432751</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.26718465598087</v>
+        <v>9.267221991604666</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.279811575040549</v>
+        <v>9.279840268486222</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.238881959468229</v>
+        <v>9.238857981288422</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.169518616385611</v>
+        <v>9.169468048323747</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.104925168824311</v>
+        <v>9.104847086403602</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.010328686479788</v>
+        <v>9.010234719222773</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.939183619710727</v>
+        <v>8.939068003906524</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.935651268662065</v>
+        <v>8.935507431120323</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.944921429694979</v>
+        <v>8.944754353722843</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.068563264665713</v>
+        <v>9.06832949843486</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.122196367726293</v>
+        <v>9.121951965845961</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.289005052692739</v>
+        <v>9.288812041642593</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.382807802096133</v>
+        <v>9.382656447432808</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.402281503048723</v>
+        <v>9.402153056471743</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.486341087450779</v>
+        <v>9.486230505130887</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.608058053281127</v>
+        <v>9.608088496492904</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.600322643097343</v>
+        <v>9.600402369377338</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.619526327077363</v>
+        <v>9.619691293687911</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.619546920368681</v>
+        <v>9.619824208982845</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.60153096048318</v>
+        <v>9.601849600335539</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.63773253945077</v>
+        <v>9.638091642172864</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.504448220004463</v>
+        <v>9.504768227885553</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.436114249288407</v>
+        <v>9.436419989275308</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.286051077981057</v>
+        <v>9.286223709944075</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.188359400086746</v>
+        <v>9.188469346461712</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.075908418395832</v>
+        <v>9.075876641746177</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.048032771179551</v>
+        <v>9.047958685806897</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.045405966656514</v>
+        <v>9.045346572071402</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.019386778336695</v>
+        <v>9.019295721446502</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>8.999044701763999</v>
+        <v>8.998951529022399</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.01138525485878</v>
+        <v>9.011339207700424</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.03963936811704</v>
+        <v>9.039655304031843</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.059831991707417</v>
+        <v>9.059882478267127</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.060800577250422</v>
+        <v>9.060803297086403</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.047590397347426</v>
+        <v>9.047580962714479</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.038329551110598</v>
+        <v>9.038299893988835</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.045568496247434</v>
+        <v>9.045500041465672</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.060867144460458</v>
+        <v>9.060762189415559</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.072196465471766</v>
+        <v>9.072035758215161</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.087220223241044</v>
+        <v>9.08709492260064</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.071387132219124</v>
+        <v>9.071275001002554</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>9.057336232985655</v>
+        <v>9.05720499166792</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>9.039255401418346</v>
+        <v>9.039148475078264</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>9.034300181007442</v>
+        <v>9.031608837304073</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>9.031853506016166</v>
+        <v>9.028530515121592</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>9.026410712979501</v>
+        <v>9.022841432396934</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>9.023600227186929</v>
+        <v>9.019354212604499</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>9.014836217416075</v>
+        <v>9.010540392572038</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>9.014606536905067</v>
+        <v>9.009719987553833</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>9.005966929913972</v>
+        <v>9.000304590536988</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>8.998139949969975</v>
+        <v>8.990994643620427</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>8.981487753681346</v>
+        <v>8.97263894022403</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>8.927781981853547</v>
+        <v>8.917507702573008</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>8.886044354709714</v>
+        <v>8.874529463462297</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>8.830362153381607</v>
+        <v>8.817182250691733</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>8.709736273122314</v>
+        <v>8.701637127845531</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>8.653633893643274</v>
+        <v>8.642166885470836</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.748718399390448</v>
+        <v>9.748723973539597</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.723951500277449</v>
+        <v>9.723963757943729</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.720957480370014</v>
+        <v>9.720974388191141</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.700355703761121</v>
+        <v>9.700382602271421</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.704866970400939</v>
+        <v>9.704893593353713</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.698112628846886</v>
+        <v>9.698138917005631</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.693937382729134</v>
+        <v>9.6939637961739</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.707996890627424</v>
+        <v>9.708023956522828</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.720588832419743</v>
+        <v>9.72062055584615</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.727339186930559</v>
+        <v>9.727363676817085</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.735994952920674</v>
+        <v>9.736019744723322</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.712380323720588</v>
+        <v>9.71240460226559</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.667995029583386</v>
+        <v>9.668019407591355</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.633914391526831</v>
+        <v>9.633944817307331</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.600645604672501</v>
+        <v>9.600665955649283</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.562772422916353</v>
+        <v>9.56279016211681</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.505027978976331</v>
+        <v>9.505066581714823</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.433571203870232</v>
+        <v>9.433625051681732</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.357644639398941</v>
+        <v>9.357694924127737</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.29020168432751</v>
+        <v>9.290254465101274</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.267221991604666</v>
+        <v>9.267258665587409</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.279840268486222</v>
+        <v>9.279868471157849</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.238857981288422</v>
+        <v>9.238834478948633</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.169468048323747</v>
+        <v>9.169418454297549</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.104847086403602</v>
+        <v>9.104770495018746</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.010234719222773</v>
+        <v>9.010142541811931</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.939068003906524</v>
+        <v>8.938954584130393</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.935507431120323</v>
+        <v>8.935366313486563</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.944754353722843</v>
+        <v>8.944590381317735</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.06832949843486</v>
+        <v>9.068100044700635</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.121951965845961</v>
+        <v>9.121712071256535</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.288812041642593</v>
+        <v>9.288622530575413</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.382656447432808</v>
+        <v>9.382507819050192</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.402153056471743</v>
+        <v>9.402026878824508</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.486230505130887</v>
+        <v>9.486121832480924</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.608088496492904</v>
+        <v>9.608118254058038</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.600402369377338</v>
+        <v>9.600480473805975</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.619691293687911</v>
+        <v>9.619853085851569</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.619824208982845</v>
+        <v>9.620096337841849</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.601849600335539</v>
+        <v>9.602162340792146</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.638091642172864</v>
+        <v>9.638444138298457</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.504768227885553</v>
+        <v>9.505082450137616</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.436419989275308</v>
+        <v>9.436720255731485</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.286223709944075</v>
+        <v>9.2863933101663</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.188469346461712</v>
+        <v>9.188577399014033</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.075876641746177</v>
+        <v>9.075845488389529</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.047958685806897</v>
+        <v>9.04788594787437</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.045346572071402</v>
+        <v>9.045288248188584</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.019295721446502</v>
+        <v>9.019206267562975</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>8.998951529022399</v>
+        <v>8.998859960771092</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.011339207700424</v>
+        <v>9.011293914735447</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.039655304031843</v>
+        <v>9.039670905939978</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.059882478267127</v>
+        <v>9.059932065308928</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.060803297086403</v>
+        <v>9.060806058454965</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.047580962714479</v>
+        <v>9.047571742539397</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.038299893988835</v>
+        <v>9.038270788787882</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.045500041465672</v>
+        <v>9.045432788501499</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.060762189415559</v>
+        <v>9.060659015633153</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.072035758215161</v>
+        <v>9.071877739807345</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.08709492260064</v>
+        <v>9.086971777975561</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.071275001002554</v>
+        <v>9.071164684615429</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>9.05720499166792</v>
+        <v>9.057075773134095</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>9.039148475078264</v>
+        <v>9.039042890721642</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>9.031608837304073</v>
+        <v>9.027662614201727</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>9.028530515121592</v>
+        <v>9.023720820703879</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>9.022841432396934</v>
+        <v>9.017475109239665</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>9.019354212604499</v>
+        <v>9.013823693731021</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>9.010540392572038</v>
+        <v>9.004464178330581</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>9.009719987553833</v>
+        <v>9.002706604266601</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>9.000304590536988</v>
+        <v>8.992196618510068</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>8.990994643620427</v>
+        <v>8.981003084895217</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>8.97263894022403</v>
+        <v>8.960450704995242</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>8.917507702573008</v>
+        <v>8.903062097172519</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>8.874529463462297</v>
+        <v>8.857688629167336</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>8.817182250691733</v>
+        <v>8.79625501934839</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>8.701637127845531</v>
+        <v>8.678655633692189</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>8.642166885470836</v>
+        <v>8.592843961210733</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.748723973539597</v>
+        <v>9.748729445419475</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.723963757943729</v>
+        <v>9.723975790842172</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.720974388191141</v>
+        <v>9.720990986465356</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.700382602271421</v>
+        <v>9.700409007734528</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.704893593353713</v>
+        <v>9.704919728226029</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.698138917005631</v>
+        <v>9.698164723187597</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.6939637961739</v>
+        <v>9.693989725084736</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.708023956522828</v>
+        <v>9.708050525290993</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.72062055584615</v>
+        <v>9.720651698249993</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.727363676817085</v>
+        <v>9.727387718785396</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.736019744723322</v>
+        <v>9.736044083087418</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.71240460226559</v>
+        <v>9.71242843683507</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.668019407591355</v>
+        <v>9.668043342039981</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.633944817307331</v>
+        <v>9.633974689567834</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.600665955649283</v>
+        <v>9.600685937725709</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.56279016211681</v>
+        <v>9.562807577242793</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.505066581714823</v>
+        <v>9.505104476934275</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.433625051681732</v>
+        <v>9.433677917264077</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.357694924127737</v>
+        <v>9.357744290622652</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.290254465101274</v>
+        <v>9.290306285880161</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.267258665587409</v>
+        <v>9.267294695319674</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.279868471157849</v>
+        <v>9.279896195451592</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.238834478948633</v>
+        <v>9.238811438500626</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.169418454297549</v>
+        <v>9.169369806505697</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.104770495018746</v>
+        <v>9.104695352454033</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.010142541811931</v>
+        <v>9.010052103699294</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.938954584130393</v>
+        <v>8.93884329853444</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.935366313486563</v>
+        <v>8.935227839494299</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.944590381317735</v>
+        <v>8.944429426891231</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.068100044700635</v>
+        <v>9.067874785354409</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.121712071256535</v>
+        <v>9.121476560554443</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.288622530575413</v>
+        <v>9.288436425300826</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.382507819050192</v>
+        <v>9.382361844100837</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.402026878824508</v>
+        <v>9.401902910749628</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.486121832480924</v>
+        <v>9.486015020800568</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.608118254058038</v>
+        <v>9.608147348134835</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.600480473805975</v>
+        <v>9.600557004894355</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.619853085851569</v>
+        <v>9.620011794023029</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.620096337841849</v>
+        <v>9.620363449427835</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.602162340792146</v>
+        <v>9.602469343908988</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.638444138298457</v>
+        <v>9.638790208230503</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.505082450137616</v>
+        <v>9.505391041993626</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.436720255731485</v>
+        <v>9.437015193994403</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.2863933101663</v>
+        <v>9.286559957508535</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.188577399014033</v>
+        <v>9.188683606003817</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.075845488389529</v>
+        <v>9.075814940310273</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.04788594787437</v>
+        <v>9.047814521060531</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.045288248188584</v>
+        <v>9.045230966425249</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.019206267562975</v>
+        <v>9.01911837489304</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>8.998859960771092</v>
+        <v>8.998769956152223</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.011293914735447</v>
+        <v>9.011249357848417</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.039670905939978</v>
+        <v>9.039686184036867</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.059932065308928</v>
+        <v>9.059980776567013</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.060806058454965</v>
+        <v>9.060808857765494</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.047571742539397</v>
+        <v>9.047562730032286</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.038270788787882</v>
+        <v>9.038242220456954</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.045432788501499</v>
+        <v>9.045366706311192</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.060659015633153</v>
+        <v>9.060557578715095</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.071877739807345</v>
+        <v>9.071722344216386</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.086971777975561</v>
+        <v>9.086850734983445</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.071164684615429</v>
+        <v>9.071056140875459</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>9.057075773134095</v>
+        <v>9.056948533461803</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>9.039042890721642</v>
+        <v>9.038938628925063</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>9.027662614201727</v>
+        <v>9.023884130911815</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>9.023720820703879</v>
+        <v>9.01930828480328</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>9.017475109239665</v>
+        <v>9.012539967647017</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>9.013823693731021</v>
+        <v>9.008623651032039</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>9.004464178330581</v>
+        <v>8.998911109099554</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>9.002706604266601</v>
+        <v>8.99637017352552</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>8.992196618510068</v>
+        <v>8.984893773663767</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>8.981003084895217</v>
+        <v>8.972014933171309</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>8.960450704995242</v>
+        <v>8.949542906322094</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>8.903062097172519</v>
+        <v>8.890325013774248</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>8.857688629167336</v>
+        <v>8.84327066203554</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>8.79625501934839</v>
+        <v>8.779480763577972</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>8.678655633692189</v>
+        <v>8.663097105078075</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>8.592843961210733</v>
+        <v>8.573472768698823</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>9.023884130911815</v>
+        <v>9.023673082685532</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>9.01930828480328</v>
+        <v>9.019056712364019</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>9.012539967647017</v>
+        <v>9.012259719153963</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>9.008623651032039</v>
+        <v>9.008324816717474</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>8.998911109099554</v>
+        <v>8.998581755912827</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>8.99637017352552</v>
+        <v>8.996002886966956</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>8.984893773663767</v>
+        <v>8.984488324075329</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>8.972014933171309</v>
+        <v>8.971547693482439</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>8.949542906322094</v>
+        <v>8.948995950375934</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>8.890325013774248</v>
+        <v>8.889653800971882</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>8.84327066203554</v>
+        <v>8.842426291204895</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>8.779480763577972</v>
+        <v>8.778260667162566</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>8.663097105078075</v>
+        <v>8.661069813169137</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>8.573472768698823</v>
+        <v>8.568889173119217</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.748729445419475</v>
+        <v>9.748734817818921</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.723975790842172</v>
+        <v>9.723987605098589</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.720990986465356</v>
+        <v>9.72100728361545</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.700409007734528</v>
+        <v>9.700434933581757</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.704919728226029</v>
+        <v>9.704945388316169</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.698164723187597</v>
+        <v>9.698190060525672</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.693989725084736</v>
+        <v>9.694015182671224</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.708050525290993</v>
+        <v>9.708076610501715</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.720651698249993</v>
+        <v>9.720682275444979</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.727387718785396</v>
+        <v>9.727411325010522</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.736044083087418</v>
+        <v>9.736067980337978</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.71242843683507</v>
+        <v>9.712451839494792</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.668043342039981</v>
+        <v>9.668066844922443</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.633974689567834</v>
+        <v>9.634004023272011</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.600685937725709</v>
+        <v>9.600705560838428</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.562807577242793</v>
+        <v>9.562824677092559</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.505104476934275</v>
+        <v>9.50514168390279</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.433677917264077</v>
+        <v>9.43372982723468</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.357744290622652</v>
+        <v>9.357792763795278</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.290306285880161</v>
+        <v>9.2903571726088</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.267294695319674</v>
+        <v>9.267330097589456</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.279896195451592</v>
+        <v>9.279923453353023</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.238811438500626</v>
+        <v>9.23878884653349</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.169369806505697</v>
+        <v>9.169322078192426</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.104695352454033</v>
+        <v>9.104621618069455</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.010052103699294</v>
+        <v>9.009963356218822</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.93884329853444</v>
+        <v>8.938734087567097</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.935227839494299</v>
+        <v>8.935091935696443</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.944429426891231</v>
+        <v>8.944271407970021</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.067874785354409</v>
+        <v>9.067653606556632</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.121476560554443</v>
+        <v>9.121245314795086</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.288436425300826</v>
+        <v>9.288253634972554</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.382361844100837</v>
+        <v>9.382218452304055</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.401902910749628</v>
+        <v>9.401781094933536</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.486015020800568</v>
+        <v>9.485910023018398</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.608147348134835</v>
+        <v>9.608175799958893</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.600557004894355</v>
+        <v>9.600632009253575</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.620011794023029</v>
+        <v>9.620167505262998</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.620363449427835</v>
+        <v>9.620625681032163</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.602469343908988</v>
+        <v>9.60277076587019</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.638790208230503</v>
+        <v>9.639130025872028</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.505391041993626</v>
+        <v>9.505694153192023</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.437015193994403</v>
+        <v>9.437304944313748</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.286559957508535</v>
+        <v>9.286723728131468</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.188683606003817</v>
+        <v>9.188788014074646</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.075814940310273</v>
+        <v>9.075784980175712</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.047814521060531</v>
+        <v>9.047744370333884</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.045230966425249</v>
+        <v>9.045174699202954</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.01911837489304</v>
+        <v>9.019032003077756</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>8.998769956152223</v>
+        <v>8.998681475674779</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.011249357848417</v>
+        <v>9.011205519489231</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.039686184036867</v>
+        <v>9.039701148113181</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.059980776567013</v>
+        <v>9.060028634951333</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.060808857765494</v>
+        <v>9.060811691643689</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.047562730032286</v>
+        <v>9.047553918675074</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.038242220456954</v>
+        <v>9.038214174480267</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.045366706311192</v>
+        <v>9.045301764899262</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.060557578715095</v>
+        <v>9.060457835706117</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.071722344216386</v>
+        <v>9.071569507523151</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.086850734983445</v>
+        <v>9.086731741026632</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.071056140875459</v>
+        <v>9.070949328837772</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>9.056948533461803</v>
+        <v>9.056823229891418</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>9.038938628925063</v>
+        <v>9.038835670355208</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>9.023673082685532</v>
+        <v>9.01985063245575</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>9.019056712364019</v>
+        <v>9.014588818515339</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>9.012259719153963</v>
+        <v>9.007265311620806</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>9.008324816717474</v>
+        <v>9.003062216048992</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>8.998581755912827</v>
+        <v>8.992966837565444</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>8.996002886966956</v>
+        <v>8.98962403551727</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>8.984488324075329</v>
+        <v>8.977172850610559</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>8.971547693482439</v>
+        <v>8.962621319152813</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>8.948995950375934</v>
+        <v>8.938264344680142</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>8.889653800971882</v>
+        <v>8.877237382821402</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>8.842426291204895</v>
+        <v>8.828551462855206</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>8.778260667162566</v>
+        <v>8.762563407175264</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>8.661069813169137</v>
+        <v>8.64702781160646</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>8.568889173119217</v>
+        <v>8.554528720721871</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.748734817818921</v>
+        <v>9.748740093426306</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.723987605098589</v>
+        <v>9.72399920661822</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.72100728361545</v>
+        <v>9.72102328776141</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.700434933581757</v>
+        <v>9.700460392761022</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.704945388316169</v>
+        <v>9.70497058644372</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.698190060525672</v>
+        <v>9.698214941679977</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.694015182671224</v>
+        <v>9.69404018166718</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.708076610501715</v>
+        <v>9.708102225235425</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.720682275444979</v>
+        <v>9.720712302676251</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.727411325010522</v>
+        <v>9.72743450723029</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.736067980337978</v>
+        <v>9.736091448357435</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.712451839494792</v>
+        <v>9.712474821877311</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.668066844922443</v>
+        <v>9.66808992780353</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.634004023272011</v>
+        <v>9.634032832849147</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.600705560838428</v>
+        <v>9.600724834570542</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.562824677092559</v>
+        <v>9.562841470148816</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.50514168390279</v>
+        <v>9.505178221195353</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.43372982723468</v>
+        <v>9.43378080725835</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.357792763795278</v>
+        <v>9.357840367664581</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.2903571726088</v>
+        <v>9.290407150305636</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.267330097589456</v>
+        <v>9.267364888607977</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.279923453353023</v>
+        <v>9.279950256453816</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.23878884653349</v>
+        <v>9.238766690148113</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.169322078192426</v>
+        <v>9.169275243598939</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.104621618069455</v>
+        <v>9.104549252728004</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.009963356218822</v>
+        <v>9.009876252499756</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.938734087567097</v>
+        <v>8.93862689386771</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.935091935696443</v>
+        <v>8.934958531336438</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.944271407970021</v>
+        <v>8.944116245055625</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.067653606556632</v>
+        <v>9.067436398545896</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.121245314795086</v>
+        <v>9.121018219293466</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.288253634972554</v>
+        <v>9.288074071941566</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.382218452304055</v>
+        <v>9.382077575834089</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.401781094933536</v>
+        <v>9.40166137601963</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.485910023018398</v>
+        <v>9.485806793624928</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.608175799958893</v>
+        <v>9.608203629889797</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.600632009253575</v>
+        <v>9.600705531686199</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.620167505262998</v>
+        <v>9.620320303395458</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.620625681032163</v>
+        <v>9.620883164989321</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.60277076587019</v>
+        <v>9.603066757251128</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.639130025872028</v>
+        <v>9.639463758915845</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.505694153192023</v>
+        <v>9.505991928217229</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.437304944313748</v>
+        <v>9.437589642071526</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.286723728131468</v>
+        <v>9.286884695609718</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.188788014074646</v>
+        <v>9.188890668320258</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.075784980175712</v>
+        <v>9.075755591304198</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.047744370333884</v>
+        <v>9.047675461896283</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.045174699202954</v>
+        <v>9.045119419904093</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.019032003077756</v>
+        <v>9.018947113131606</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>8.998681475674779</v>
+        <v>8.99859448115831</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.011205519489231</v>
+        <v>9.011162382651703</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.039701148113181</v>
+        <v>9.039715807574506</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.060028634951333</v>
+        <v>9.060075662582891</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.060811691643689</v>
+        <v>9.060814556918126</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.047553918675074</v>
+        <v>9.047545302208446</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.038214174480267</v>
+        <v>9.038186636853791</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.045301764899262</v>
+        <v>9.0452379352751</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.060457835706117</v>
+        <v>9.060359745036619</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.071569507523151</v>
+        <v>9.071419167838904</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.086731741026632</v>
+        <v>9.086614745220878</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.070949328837772</v>
+        <v>9.070844208752844</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>9.056823229891418</v>
+        <v>9.056699820793025</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>9.038835670355208</v>
+        <v>9.038733995790869</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>9.01985063245575</v>
+        <v>9.017031621462536</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>9.014588818515339</v>
+        <v>9.011273975294955</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>9.007265311620806</v>
+        <v>9.003524200254178</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>9.003062216048992</v>
+        <v>8.999180589674026</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>8.992966837565444</v>
+        <v>8.988864274352569</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>8.98962403551727</v>
+        <v>8.984961296222041</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>8.977172850610559</v>
+        <v>8.971805202289278</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>8.962621319152813</v>
+        <v>8.956028020255649</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>8.938264344680142</v>
+        <v>8.930380381688657</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>8.877237382821402</v>
+        <v>8.868443929205675</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>8.828551462855206</v>
+        <v>8.819318982903525</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>8.762563407175264</v>
+        <v>8.753556333324116</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>8.64702781160646</v>
+        <v>8.642980309065894</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>8.554528720721871</v>
+        <v>8.558723032983018</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B118"/>
+  <dimension ref="A1:B119"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.748740093426306</v>
+        <v>9.748745274833995</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.72399920661822</v>
+        <v>9.724010601095541</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.72102328776141</v>
+        <v>9.721039006733903</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.700460392761022</v>
+        <v>9.700485397758397</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.70497058644372</v>
+        <v>9.704995334970929</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.698214941679977</v>
+        <v>9.698239378858945</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.69404018166718</v>
+        <v>9.694064734351858</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.708102225235425</v>
+        <v>9.708127382105067</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.720712302676251</v>
+        <v>9.720741794645678</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.72743450723029</v>
+        <v>9.727457276764763</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.736091448357435</v>
+        <v>9.736114498605311</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.712474821877311</v>
+        <v>9.712497395201245</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.66808992780353</v>
+        <v>9.668112601838619</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.634032832849147</v>
+        <v>9.634061132217809</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.600724834570542</v>
+        <v>9.600743768167167</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.562841470148816</v>
+        <v>9.562857964592729</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.505178221195353</v>
+        <v>9.505214106724711</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.43378080725835</v>
+        <v>9.433830882089502</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.357840367664581</v>
+        <v>9.357887125396511</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.290407150305636</v>
+        <v>9.290456243103879</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.267364888607977</v>
+        <v>9.267399084034178</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.279950256453816</v>
+        <v>9.279976615967655</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.238766690148113</v>
+        <v>9.2387449569331</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.169275243598939</v>
+        <v>9.169229277917513</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.104549252728004</v>
+        <v>9.104478218726936</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.009876252499756</v>
+        <v>9.00979074738478</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.93862689386771</v>
+        <v>8.938521662166892</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.934958531336438</v>
+        <v>8.934827558226416</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.944116245055625</v>
+        <v>8.943963861491591</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.067436398545896</v>
+        <v>9.067223055458124</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.121018219293466</v>
+        <v>9.120795163435414</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.288074071941566</v>
+        <v>9.287897651616886</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.382077575834089</v>
+        <v>9.381939149214109</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.40166137601963</v>
+        <v>9.40154370052587</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.485806793624928</v>
+        <v>9.485705288608976</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.608203629889797</v>
+        <v>9.608230857455071</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.600705531686199</v>
+        <v>9.600777615272552</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.620320303395458</v>
+        <v>9.620470269156298</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.620883164989321</v>
+        <v>9.621136028898345</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.603066757251128</v>
+        <v>9.603357463267567</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.639463758915845</v>
+        <v>9.639791569118954</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.505991928217229</v>
+        <v>9.506284506527713</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.437589642071526</v>
+        <v>9.437869417990939</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.286884695609718</v>
+        <v>9.28704293104019</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.188890668320258</v>
+        <v>9.188991612347989</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.075755591304198</v>
+        <v>9.075726757635042</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.047675461896283</v>
+        <v>9.047607763129296</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.045119419904093</v>
+        <v>9.045065102830565</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.018947113131606</v>
+        <v>9.018863667384823</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>8.99859448115831</v>
+        <v>8.9985089356794</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.011162382651703</v>
+        <v>9.011119930853162</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.039715807574506</v>
+        <v>9.039730171459858</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.060075662582891</v>
+        <v>9.060121880827282</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.060814556918126</v>
+        <v>9.060817450607711</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.047545302208446</v>
+        <v>9.047536874619547</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.038186636853791</v>
+        <v>9.038159594063183</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.0452379352751</v>
+        <v>9.045175189411742</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.060359745036619</v>
+        <v>9.060263266468089</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.071419167838904</v>
+        <v>9.071271265226619</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.086614745220878</v>
+        <v>9.08649969832738</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.070844208752844</v>
+        <v>9.070740742026</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>9.056699820793025</v>
+        <v>9.056578265634206</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>9.038733995790869</v>
+        <v>9.038633586142513</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>9.017031621462536</v>
+        <v>9.017045554761836</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>9.011273975294955</v>
+        <v>9.008397700406912</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>9.003524200254178</v>
+        <v>9.000519005025392</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>8.999180589674026</v>
+        <v>8.995794090082647</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>8.988864274352569</v>
+        <v>8.984813022319639</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>8.984961296222041</v>
+        <v>8.980538609224979</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>8.971805202289278</v>
+        <v>8.966889954108435</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>8.956028020255649</v>
+        <v>8.950096064420574</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>8.930380381688657</v>
+        <v>8.923306210806331</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>8.868443929205675</v>
+        <v>8.8613522739583</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>8.819318982903525</v>
+        <v>8.810900942534829</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>8.753556333324116</v>
+        <v>8.745412142970302</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>8.642980309065894</v>
+        <v>8.639286967202631</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,15 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>8.558723032983018</v>
+        <v>8.560959647955253</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119" s="3">
+        <v>46388</v>
+      </c>
+      <c r="B119">
+        <v>8.534242226827301</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.748745274833995</v>
+        <v>9.748750364542598</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.724010601095541</v>
+        <v>9.724021794023605</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.721039006733903</v>
+        <v>9.721054448087052</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.700485397758397</v>
+        <v>9.700509960618517</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.704995334970929</v>
+        <v>9.705019645822917</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.698239378858945</v>
+        <v>9.698263383839294</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.694064734351858</v>
+        <v>9.694088852570063</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.708127382105067</v>
+        <v>9.708152093276778</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.720741794645678</v>
+        <v>9.720770765535866</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.727457276764763</v>
+        <v>9.727479644534663</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.736114498605311</v>
+        <v>9.736137142136876</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.712497395201245</v>
+        <v>9.712519570289512</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.668112601838619</v>
+        <v>9.668134877791596</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.634061132217809</v>
+        <v>9.634088934808219</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.600743768167167</v>
+        <v>9.600762370550196</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.562857964592729</v>
+        <v>9.562874168317206</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.505214106724711</v>
+        <v>9.505249357770605</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.433830882089502</v>
+        <v>9.433880075612148</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.357887125396511</v>
+        <v>9.357933059341519</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.290456243103879</v>
+        <v>9.290504474290303</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.267399084034178</v>
+        <v>9.267432698997972</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.279976615967655</v>
+        <v>9.280002542745354</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.2387449569331</v>
+        <v>9.238723634942021</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.169229277917513</v>
+        <v>9.169184157248065</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.104478218726936</v>
+        <v>9.104408479732797</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.00979074738478</v>
+        <v>9.009706797352539</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.938521662166892</v>
+        <v>8.938418339192246</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.934827558226416</v>
+        <v>8.934698950631889</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.943963861491591</v>
+        <v>8.943814183337743</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.067223055458124</v>
+        <v>9.067013475155319</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.120795163435414</v>
+        <v>9.120576040498751</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.287897651616886</v>
+        <v>9.287724292333598</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.381939149214109</v>
+        <v>9.38180310921561</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.40154370052587</v>
+        <v>9.40142801676642</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.485705288608976</v>
+        <v>9.485605465397004</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.608230857455071</v>
+        <v>9.608257501391535</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.600777615272552</v>
+        <v>9.600848301452128</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.620470269156298</v>
+        <v>9.620617480333834</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.621136028898345</v>
+        <v>9.621384395832479</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.603357463267567</v>
+        <v>9.603643024011642</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.639791569118954</v>
+        <v>9.640113612562516</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.506284506527713</v>
+        <v>9.506572022772234</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.437869417990939</v>
+        <v>9.438144398334558</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.28704293104019</v>
+        <v>9.28719850314504</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.188991612347989</v>
+        <v>9.18909088833913</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.075726757635042</v>
+        <v>9.075698463700045</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.047607763129296</v>
+        <v>9.047541242543311</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.045065102830565</v>
+        <v>9.045011723164579</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.018863667384823</v>
+        <v>9.018781629428599</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>8.9985089356794</v>
+        <v>8.998424803520685</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.011119930853162</v>
+        <v>9.011078148114848</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.039730171459858</v>
+        <v>9.039744248459174</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.060121880827282</v>
+        <v>9.060167310326523</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.060817450607711</v>
+        <v>9.060820369909973</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.047536874619547</v>
+        <v>9.047528630130326</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.038159594063183</v>
+        <v>9.038133033062845</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.045175189411742</v>
+        <v>9.04511350020662</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.060263266468089</v>
+        <v>9.060168361041054</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.071271265226619</v>
+        <v>9.071125741625881</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.08649969832738</v>
+        <v>9.086386552687973</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.070740742026</v>
+        <v>9.070638891178341</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>9.056578265634206</v>
+        <v>9.056458524948564</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>9.038633586142513</v>
+        <v>9.038534422469622</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>9.017045554761836</v>
+        <v>9.017058653867899</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>9.008397700406912</v>
+        <v>9.005101241858286</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>9.000519005025392</v>
+        <v>8.996993681052441</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>8.995794090082647</v>
+        <v>8.99187307537666</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>8.984813022319639</v>
+        <v>8.980220604014072</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>8.980538609224979</v>
+        <v>8.97547335656996</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>8.966889954108435</v>
+        <v>8.96125419877311</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>8.950096064420574</v>
+        <v>8.943346016624691</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>8.923306210806331</v>
+        <v>8.915299722165816</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>8.8613522739583</v>
+        <v>8.85311487626668</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>8.810900942534829</v>
+        <v>8.801107937999744</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>8.745412142970302</v>
+        <v>8.73538552022557</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>8.639286967202631</v>
+        <v>8.63216544600062</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>8.560959647955253</v>
+        <v>8.556120502818414</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>8.534242226827301</v>
+        <v>8.508134769627912</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>9.005101241858286</v>
+        <v>9.005721985031272</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>8.996993681052441</v>
+        <v>8.997774511214569</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>8.99187307537666</v>
+        <v>8.992763719911206</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>8.980220604014072</v>
+        <v>8.981550741056871</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>8.97547335656996</v>
+        <v>8.976802890610047</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>8.96125419877311</v>
+        <v>8.962585007942883</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>8.943346016624691</v>
+        <v>8.944777093012123</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>8.915299722165816</v>
+        <v>8.916894157934628</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>8.85311487626668</v>
+        <v>8.854944005700602</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>8.801107937999744</v>
+        <v>8.80331523050951</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>8.73538552022557</v>
+        <v>8.738242491072775</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>8.63216544600062</v>
+        <v>8.636180962811352</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>8.556120502818414</v>
+        <v>8.562494091182813</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>8.508134769627912</v>
+        <v>8.533201222269229</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.748750364542598</v>
+        <v>9.748755364965</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.724021794023605</v>
+        <v>9.724032790702863</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.721054448087052</v>
+        <v>9.72106961911053</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.700509960618517</v>
+        <v>9.70053409296391</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.705019645822917</v>
+        <v>9.705043530506806</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.698263383839294</v>
+        <v>9.698286967984922</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.694088852570063</v>
+        <v>9.694112547751192</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.708152093276778</v>
+        <v>9.708176370489511</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.720770765535866</v>
+        <v>9.720799229032862</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.727479644534663</v>
+        <v>9.727501621078833</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.736137142136876</v>
+        <v>9.736159389620813</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.712519570289512</v>
+        <v>9.712541357586636</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.668134877791596</v>
+        <v>9.668156766051903</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.634088934808219</v>
+        <v>9.63411625358348</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.600762370550196</v>
+        <v>9.600780650332322</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.562874168317206</v>
+        <v>9.562890088939477</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.505249357770605</v>
+        <v>9.505283991007499</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.433880075612148</v>
+        <v>9.433928410877803</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.357933059341519</v>
+        <v>9.357978191070117</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.290504474290303</v>
+        <v>9.290551866342017</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.267432698997972</v>
+        <v>9.267465748122341</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.280002542745354</v>
+        <v>9.280028047289321</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.238723634942021</v>
+        <v>9.23870271267193</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.169184157248065</v>
+        <v>9.169139858557138</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.104408479732797</v>
+        <v>9.104340000719917</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.009706797352539</v>
+        <v>9.009624360444363</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.938418339192246</v>
+        <v>8.938316873579137</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.934698950631889</v>
+        <v>8.934572645162575</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.943814183337743</v>
+        <v>8.943667139251048</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.067013475155319</v>
+        <v>9.066807559063221</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.120576040498751</v>
+        <v>9.120360747483794</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.287724292333598</v>
+        <v>9.287553915227601</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.38180310921561</v>
+        <v>9.381669394762952</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.40142801676642</v>
+        <v>9.401314274777206</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.485605465397004</v>
+        <v>9.485507282795416</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.608257501391535</v>
+        <v>9.60828357968423</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.600848301452128</v>
+        <v>9.600917630100469</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.620617480333834</v>
+        <v>9.620762011901764</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.621384395832479</v>
+        <v>9.621628384537784</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.603643024011642</v>
+        <v>9.603923574675512</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.640113612562516</v>
+        <v>9.640430039898321</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.506572022772234</v>
+        <v>9.506854606995098</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.438144398334558</v>
+        <v>9.438414705092534</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.28719850314504</v>
+        <v>9.287351478369606</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.18909088833913</v>
+        <v>9.189188537106423</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.075698463700045</v>
+        <v>9.075670694596599</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.047541242543311</v>
+        <v>9.04747586972929</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.045011723164579</v>
+        <v>9.044959256931417</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.018781629428599</v>
+        <v>9.018700964062976</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>8.998424803520685</v>
+        <v>8.998342050122348</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.011078148114848</v>
+        <v>9.011037018943231</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.039744248459174</v>
+        <v>9.039758046929808</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.060167310326523</v>
+        <v>9.060211971029302</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.060820369909973</v>
+        <v>9.060823312190166</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.047528630130326</v>
+        <v>9.047520563186549</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.038133033062845</v>
+        <v>9.038106941256029</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.04511350020662</v>
+        <v>9.045052841444184</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.060168361041054</v>
+        <v>9.060074991025406</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.071125741625881</v>
+        <v>9.070982540781159</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.086386552687973</v>
+        <v>9.086275262163252</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.070638891178341</v>
+        <v>9.070538619809112</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>9.056458524948564</v>
+        <v>9.056340560305067</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>9.038534422469622</v>
+        <v>9.038436485995998</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>9.017058653867899</v>
+        <v>9.017070955069567</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>9.005721985031272</v>
+        <v>9.002212424846089</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>8.997774511214569</v>
+        <v>8.993977608346786</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>8.992763719911206</v>
+        <v>8.988543348575</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>8.981550741056871</v>
+        <v>8.977058644508453</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>8.976802890610047</v>
+        <v>8.97166837890563</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>8.962585007942883</v>
+        <v>8.956766154501976</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>8.944777093012123</v>
+        <v>8.937761504991904</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>8.916894157934628</v>
+        <v>8.908549245977373</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>8.854944005700602</v>
+        <v>8.846226364192162</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>8.80331523050951</v>
+        <v>8.792925297199069</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>8.738242491072775</v>
+        <v>8.727324589550093</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>8.636180962811352</v>
+        <v>8.627200005326864</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>8.562494091182813</v>
+        <v>8.553876026719625</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>8.533201222269229</v>
+        <v>8.503544958871988</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.748755364965</v>
+        <v>9.748760278430169</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.724032790702863</v>
+        <v>9.72404359624953</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.72106961911053</v>
+        <v>9.721084526841032</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.70053409296391</v>
+        <v>9.700557806013332</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.705043530506806</v>
+        <v>9.705067000129903</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.698286967984922</v>
+        <v>9.698310142264855</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.694112547751192</v>
+        <v>9.694135830927285</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.708176370489511</v>
+        <v>9.708200225073615</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.720799229032862</v>
+        <v>9.720827198347697</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.727501621078833</v>
+        <v>9.727523216570766</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.736159389620813</v>
+        <v>9.736181251355957</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.712541357586636</v>
+        <v>9.712562767175122</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.668156766051903</v>
+        <v>9.668178276650652</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.63411625358348</v>
+        <v>9.634143101059701</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.600780650332322</v>
+        <v>9.600798615830282</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.562890088939477</v>
+        <v>9.562905733813027</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.505283991007499</v>
+        <v>9.505318022530819</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.433928410877803</v>
+        <v>9.433975910141426</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.357978191070117</v>
+        <v>9.35802254140658</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.290551866342017</v>
+        <v>9.290598440961331</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.267465748122341</v>
+        <v>9.267498245544335</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.280028047289321</v>
+        <v>9.280053139767277</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.23870271267193</v>
+        <v>9.238682179043067</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.169139858557138</v>
+        <v>9.169096359639038</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.104340000719917</v>
+        <v>9.104272747912187</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.009624360444363</v>
+        <v>9.009543396194877</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.938316873579137</v>
+        <v>8.938217215786203</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.934572645162575</v>
+        <v>8.934448580669024</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.943667139251048</v>
+        <v>8.943522660372672</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.066807559063221</v>
+        <v>9.066605212017379</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.120360747483794</v>
+        <v>9.120149184952616</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.287553915227601</v>
+        <v>9.287386444116772</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.381669394762952</v>
+        <v>9.381537946842686</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.401314274777206</v>
+        <v>9.401202426245119</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.485507282795416</v>
+        <v>9.485410700935546</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.60828357968423</v>
+        <v>9.608309109603143</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.600917630100469</v>
+        <v>9.600985639601767</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.620762011901764</v>
+        <v>9.62090393614498</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.621628384537784</v>
+        <v>9.621868109621431</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.603923574675512</v>
+        <v>9.604199245763386</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.640430039898321</v>
+        <v>9.640740996582524</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.506854606995098</v>
+        <v>9.507132384830976</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.438414705092534</v>
+        <v>9.43868045616135</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.287351478369606</v>
+        <v>9.287501920975489</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.189188537106423</v>
+        <v>9.18928459814877</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.075670694596599</v>
+        <v>9.075643435962203</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.04747586972929</v>
+        <v>9.047411615312919</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.044959256931417</v>
+        <v>9.044907680964073</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.018700964062976</v>
+        <v>9.018621637247314</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>8.998342050122348</v>
+        <v>8.998260642035909</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.011037018943231</v>
+        <v>9.010996528312083</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.039758046929808</v>
+        <v>9.039771574912116</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.060211971029302</v>
+        <v>9.060255882219728</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.060823312190166</v>
+        <v>9.060826274971069</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.047520563186549</v>
+        <v>9.047512668447382</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.038106941256029</v>
+        <v>9.03808130647594</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.045052841444184</v>
+        <v>9.044993187760307</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.060074991025406</v>
+        <v>9.059983119872985</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.070982540781159</v>
+        <v>9.070841608173275</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.086275262163252</v>
+        <v>9.086165782073568</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.070538619809112</v>
+        <v>9.070439892559424</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>9.056340560305067</v>
+        <v>9.056224334278131</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>9.038436485995998</v>
+        <v>9.038339758123222</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>9.017070955069567</v>
+        <v>9.017082492947669</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>9.002212424846089</v>
+        <v>8.998840492420616</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>8.993977608346786</v>
+        <v>8.990337899441336</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>8.988543348575</v>
+        <v>8.984510779541813</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>8.977058644508453</v>
+        <v>8.972781137627205</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>8.97166837890563</v>
+        <v>8.966762680032268</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>8.956766154501976</v>
+        <v>8.951209432228726</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>8.937761504991904</v>
+        <v>8.931085792771707</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>8.908549245977373</v>
+        <v>8.900653240535309</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>8.846226364192162</v>
+        <v>8.838042973389975</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>8.792925297199069</v>
+        <v>8.7832865122471</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>8.727324589550093</v>
+        <v>8.717425029062877</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>8.627200005326864</v>
+        <v>8.619349149521057</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>8.553876026719625</v>
+        <v>8.546854987062712</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>8.503544958871988</v>
+        <v>8.488387457311294</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.748760278430169</v>
+        <v>9.74876510718677</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.72404359624953</v>
+        <v>9.724054215603523</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.721084526841032</v>
+        <v>9.72109917807316</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.700557806013332</v>
+        <v>9.700581110599146</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.705067000129903</v>
+        <v>9.705090065416883</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.698310142264855</v>
+        <v>9.698332917270234</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.694135830927285</v>
+        <v>9.694158712750136</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.708200225073615</v>
+        <v>9.70822366796844</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.720827198347697</v>
+        <v>9.720854686236809</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.727523216570766</v>
+        <v>9.727544440834311</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.736181251355957</v>
+        <v>9.73620273728719</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.712562767175122</v>
+        <v>9.712583808791013</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.668178276650652</v>
+        <v>9.668199419275956</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.634143101059701</v>
+        <v>9.634169489325101</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.600798615830282</v>
+        <v>9.600816275077477</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.562905733813027</v>
+        <v>9.562921110038902</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.505318022530819</v>
+        <v>9.505351467881882</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.433975910141426</v>
+        <v>9.434022594895502</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.35802254140658</v>
+        <v>9.358066130460932</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.290598440961331</v>
+        <v>9.290644219108849</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.267498245544335</v>
+        <v>9.267530204935049</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.280053139767277</v>
+        <v>9.280077830025393</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.238682179043067</v>
+        <v>9.238662023379632</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.169096359639038</v>
+        <v>9.169053639079053</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.104272747912187</v>
+        <v>9.104206688727942</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.009543396194877</v>
+        <v>9.009463865566261</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.938217215786203</v>
+        <v>8.938119318015303</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.934448580669024</v>
+        <v>8.93432669814462</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.943522660372672</v>
+        <v>8.943380680220915</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.066605212017379</v>
+        <v>9.066406342117141</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.120149184952616</v>
+        <v>9.119941256876579</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.287386444116772</v>
+        <v>9.287221805388064</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.381537946842686</v>
+        <v>9.381408708417432</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.401202426245119</v>
+        <v>9.401092424440648</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.485410700935546</v>
+        <v>9.485315681221255</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.608309109603143</v>
+        <v>9.608334107737786</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.600985639601767</v>
+        <v>9.601052366917489</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.62090393614498</v>
+        <v>9.621043322778743</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.621868109621431</v>
+        <v>9.622103681730245</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.604199245763386</v>
+        <v>9.604470163292699</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.640740996582524</v>
+        <v>9.641046623097434</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.507132384830976</v>
+        <v>9.507405477689945</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.43868045616135</v>
+        <v>9.438941765513723</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.287501920975489</v>
+        <v>9.287649893129213</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.18928459814877</v>
+        <v>9.189379109703388</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.075643435962203</v>
+        <v>9.075616673950364</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.047411615312919</v>
+        <v>9.0473484509111</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.044907680964073</v>
+        <v>9.04485697286966</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.018621637247314</v>
+        <v>9.018543616053147</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>8.998260642035909</v>
+        <v>8.998180546880183</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.010996528312083</v>
+        <v>9.01095666164535</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.039771574912116</v>
+        <v>9.039784840144168</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.060255882219728</v>
+        <v>9.06029906254466</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.060826274971069</v>
+        <v>9.060829255923458</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.047512668447382</v>
+        <v>9.047504940775562</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.03808130647594</v>
+        <v>9.038056116967764</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.044993187760307</v>
+        <v>9.044934514608368</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.059983119872985</v>
+        <v>9.059892712172298</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.070841608173275</v>
+        <v>9.070702890953918</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.086165782073568</v>
+        <v>9.08605806914268</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.070439892559424</v>
+        <v>9.070342675077312</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>9.056224334278131</v>
+        <v>9.056109810418537</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>9.038339758123222</v>
+        <v>9.038244220442449</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>9.017082492947669</v>
+        <v>9.017093300465092</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>8.998840492420616</v>
+        <v>8.996050946001743</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>8.990337899441336</v>
+        <v>8.987409377202869</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>8.984510779541813</v>
+        <v>8.98129467840948</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>8.972781137627205</v>
+        <v>8.969362099887006</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>8.966762680032268</v>
+        <v>8.962801041521052</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>8.951209432228726</v>
+        <v>8.946687942139567</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>8.931085792771707</v>
+        <v>8.92562732138882</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>8.900653240535309</v>
+        <v>8.894213828835777</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>8.838042973389975</v>
+        <v>8.831564504856763</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>8.7832865122471</v>
+        <v>8.775779613791002</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>8.717425029062877</v>
+        <v>8.710249252928129</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>8.619349149521057</v>
+        <v>8.614877361194674</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>8.546854987062712</v>
+        <v>8.544506521154629</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>8.488387457311294</v>
+        <v>8.486650671897598</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.74876510718677</v>
+        <v>9.748769853406607</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.724054215603523</v>
+        <v>9.724064653535985</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.72109917807316</v>
+        <v>9.72111357936973</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.700581110599146</v>
+        <v>9.70060401718381</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.705090065416883</v>
+        <v>9.705112736726146</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.698332917270234</v>
+        <v>9.698355303230461</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.694158712750136</v>
+        <v>9.694181203507544</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.70822366796844</v>
+        <v>9.708246709739088</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.720854686236809</v>
+        <v>9.720881705021428</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.727544440834311</v>
+        <v>9.727565303358556</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.73620273728719</v>
+        <v>9.736223857020521</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.712583808791013</v>
+        <v>9.712604491838642</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.668199419275956</v>
+        <v>9.668220203287452</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.634169489325101</v>
+        <v>9.634195430058131</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.600816275077477</v>
+        <v>9.600833635835926</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.562921110038902</v>
+        <v>9.562936224476459</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.505351467881882</v>
+        <v>9.505384342071519</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.434022594895502</v>
+        <v>9.434068485902426</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.358066130460932</v>
+        <v>9.358108977659292</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.290644219108849</v>
+        <v>9.290689221034883</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.267530204935049</v>
+        <v>9.267561639518597</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.280077830025393</v>
+        <v>9.280102127600784</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.238662023379632</v>
+        <v>9.238642235391611</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.169053639079053</v>
+        <v>9.169011676218618</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.104206688727942</v>
+        <v>9.104141791727677</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.009463865566261</v>
+        <v>9.009385730885958</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.938119318015303</v>
+        <v>8.938023134135635</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.93432669814462</v>
+        <v>8.934206940632709</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.943380680220915</v>
+        <v>8.943241134589577</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.066406342117141</v>
+        <v>9.066210860587047</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.119941256876579</v>
+        <v>9.119736870491602</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.287221805388064</v>
+        <v>9.287059927890297</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.381408708417432</v>
+        <v>9.381281624344023</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.401092424440648</v>
+        <v>9.40098422415381</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.485315681221255</v>
+        <v>9.485222186278946</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.608334107737786</v>
+        <v>9.608358590029837</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.601052366917489</v>
+        <v>9.601117847651279</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.621043322778743</v>
+        <v>9.621180239061559</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.622103681730245</v>
+        <v>9.622335207720072</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.604470163292699</v>
+        <v>9.604736448984992</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.641046623097434</v>
+        <v>9.641347055162051</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.507405477689945</v>
+        <v>9.507674002933284</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.438941765513723</v>
+        <v>9.43919874336013</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.287649893129213</v>
+        <v>9.287795454986536</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.189379109703388</v>
+        <v>9.189472108795512</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.075616673950364</v>
+        <v>9.075590395207755</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.0473484509111</v>
+        <v>9.047286349090605</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.04485697286966</v>
+        <v>9.044807110997439</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.018543616053147</v>
+        <v>9.018466868619299</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>8.998180546880183</v>
+        <v>8.998101733299309</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.01095666164535</v>
+        <v>9.010917404800725</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.039784840144168</v>
+        <v>9.039797850075683</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.06029906254466</v>
+        <v>9.060341530039718</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.060829255923458</v>
+        <v>9.060832252857219</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.047504940775562</v>
+        <v>9.047497375228069</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.038056116967764</v>
+        <v>9.038031361371594</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.044934514608368</v>
+        <v>9.044876798226923</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.059892712172298</v>
+        <v>9.05980373360528</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.070702890953918</v>
+        <v>9.070566337883067</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.08605806914268</v>
+        <v>9.085952081443944</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.070342675077312</v>
+        <v>9.070246933984048</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>9.056109810418537</v>
+        <v>9.055996953225099</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>9.038244220442449</v>
+        <v>9.038149854744653</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>9.017093300465092</v>
+        <v>9.017103409051558</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>8.996050946001743</v>
+        <v>8.993367480770715</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>8.987409377202869</v>
+        <v>8.984601834064307</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>8.98129467840948</v>
+        <v>8.978230488851036</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>8.969362099887006</v>
+        <v>8.966128196107775</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>8.962801041521052</v>
+        <v>8.95901749214703</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>8.946687942139567</v>
+        <v>8.942366546276229</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>8.92562732138882</v>
+        <v>8.920424307521195</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>8.894213828835777</v>
+        <v>8.888105424973817</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>8.831564504856763</v>
+        <v>8.825460924163366</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>8.775779613791002</v>
+        <v>8.768777506698587</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>8.710249252928129</v>
+        <v>8.703675678006052</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>8.614877361194674</v>
+        <v>8.610873028366077</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>8.544506521154629</v>
+        <v>8.542449068036692</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>8.486650671897598</v>
+        <v>8.485292181644303</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B119"/>
+  <dimension ref="A1:B120"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.748769853406607</v>
+        <v>9.748774519187865</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.724064653535985</v>
+        <v>9.724074914656446</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.72111357936973</v>
+        <v>9.721127737071592</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.70060401718381</v>
+        <v>9.700626535875529</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.705112736726146</v>
+        <v>9.70513502406531</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.698355303230461</v>
+        <v>9.698377310028492</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.694181203507544</v>
+        <v>9.694203313138717</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.708246709739088</v>
+        <v>9.708269360592256</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.720881705021428</v>
+        <v>9.720908266605976</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.727565303358556</v>
+        <v>9.727585813311961</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.736223857020521</v>
+        <v>9.73624461983737</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.712604491838642</v>
+        <v>9.71262482540463</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.668220203287452</v>
+        <v>9.668240637730106</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.634195430058131</v>
+        <v>9.634220934544681</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.600833635835926</v>
+        <v>9.600850705607622</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.562936224476459</v>
+        <v>9.562951083753553</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.505384342071519</v>
+        <v>9.505416659602524</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.434068485902426</v>
+        <v>9.434113603225207</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.358108977659292</v>
+        <v>9.358151101772696</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.290689221034883</v>
+        <v>9.290733466309259</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.267561639518597</v>
+        <v>9.267592562090206</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.280102127600784</v>
+        <v>9.280126041733451</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.238642235391611</v>
+        <v>9.238622805157586</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.169011676218618</v>
+        <v>9.168970451122304</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.104141791727677</v>
+        <v>9.104078026564554</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.009385730885958</v>
+        <v>9.009308955787599</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.938023134135635</v>
+        <v>8.937928619611789</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.934206940632709</v>
+        <v>8.93408925313847</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.943241134589577</v>
+        <v>8.943103961451531</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.066210860587047</v>
+        <v>9.066018681645247</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.119736870491602</v>
+        <v>9.119535936160744</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.287059927890297</v>
+        <v>9.286900742832248</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.381281624344023</v>
+        <v>9.381156641295675</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.40098422415381</v>
+        <v>9.400877781633103</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.485222186278946</v>
+        <v>9.485130179909927</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.608358590029837</v>
+        <v>9.60838257180392</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.601117847651279</v>
+        <v>9.601182116110333</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.621180239061559</v>
+        <v>9.621314749902186</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.622335207720072</v>
+        <v>9.622562790816584</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.604736448984992</v>
+        <v>9.604998220447154</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.641347055162051</v>
+        <v>9.641642423932009</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.507674002933284</v>
+        <v>9.507938074040595</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.43919874336013</v>
+        <v>9.439451496302413</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.287795454986536</v>
+        <v>9.28793866477281</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.189472108795512</v>
+        <v>9.189563631285754</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.075590395207755</v>
+        <v>9.075564586852577</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.047286349090605</v>
+        <v>9.047225283328771</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.044807110997439</v>
+        <v>9.044758074408465</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.018466868619299</v>
+        <v>9.018391364109178</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>8.998101733299309</v>
+        <v>8.998024170922733</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.010917404800725</v>
+        <v>9.010878744053944</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.039797850075683</v>
+        <v>9.039810611881176</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.060341530039718</v>
+        <v>9.060383302154033</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.060832252857219</v>
+        <v>9.060835263713006</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.047497375228069</v>
+        <v>9.047489967047305</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.038031361371594</v>
+        <v>9.038007028706167</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.044876798226923</v>
+        <v>9.0448200156089</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.05980373360528</v>
+        <v>9.059716150905992</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.070566337883067</v>
+        <v>9.070431899269131</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.085952081443944</v>
+        <v>9.085847778348924</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.070246933984048</v>
+        <v>9.070152636841716</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>9.055996953225099</v>
+        <v>9.055885728117126</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>9.038149854744653</v>
+        <v>9.038056643029513</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>9.017103409051558</v>
+        <v>9.017112848683443</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>8.993367480770715</v>
+        <v>8.993463366519263</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>8.984601834064307</v>
+        <v>8.982556444329099</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>8.978230488851036</v>
+        <v>8.976276996489144</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>8.966128196107775</v>
+        <v>8.964350679376759</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>8.95901749214703</v>
+        <v>8.956342478338936</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>8.942366546276229</v>
+        <v>8.939362725209383</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>8.920424307521195</v>
+        <v>8.916781332100278</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>8.888105424973817</v>
+        <v>8.883950185561211</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>8.825460924163366</v>
+        <v>8.821841013496822</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>8.768777506698587</v>
+        <v>8.766167023507364</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>8.703675678006052</v>
+        <v>8.702085132418716</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>8.610873028366077</v>
+        <v>8.613518191346262</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>8.542449068036692</v>
+        <v>8.549638055230993</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,15 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>8.485292181644303</v>
+        <v>8.501085928899458</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120" s="3">
+        <v>46395</v>
+      </c>
+      <c r="B120">
+        <v>8.5481439706695</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>8.976276996489144</v>
+        <v>8.976285642599763</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>8.964350679376759</v>
+        <v>8.964378479185276</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>8.956342478338936</v>
+        <v>8.956684276747481</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>8.939362725209383</v>
+        <v>8.939650559146056</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>8.916781332100278</v>
+        <v>8.917003119824802</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>8.883950185561211</v>
+        <v>8.884124541277508</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>8.821841013496822</v>
+        <v>8.821983797260355</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>8.766167023507364</v>
+        <v>8.766295086362963</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>8.702085132418716</v>
+        <v>8.702239367479761</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>8.613518191346262</v>
+        <v>8.613689183990296</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>8.549638055230993</v>
+        <v>8.549841818227815</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>8.501085928899458</v>
+        <v>8.50140665797975</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46395</v>
       </c>
       <c r="B120">
-        <v>8.5481439706695</v>
+        <v>8.550049716308807</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.748774519187865</v>
+        <v>9.748779106558217</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.724074914656446</v>
+        <v>9.724085003419583</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.721127737071592</v>
+        <v>9.721141657306918</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.700626535875529</v>
+        <v>9.700648676443132</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.70513502406531</v>
+        <v>9.705156937105929</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.698377310028492</v>
+        <v>9.6983989472154</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.694203313138717</v>
+        <v>9.694225051248919</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.708269360592256</v>
+        <v>9.708291630391315</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.720908266605976</v>
+        <v>9.720934382495539</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.727585813311961</v>
+        <v>9.727605979555808</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.73624461983737</v>
+        <v>9.7362650347082</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.71262482540463</v>
+        <v>9.712644818271201</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.668240637730106</v>
+        <v>9.668260731347321</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.634220934544681</v>
+        <v>9.634246013694433</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.600850705607622</v>
+        <v>9.600867491645326</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.562951083753553</v>
+        <v>9.56296569427621</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.505416659602524</v>
+        <v>9.505448434490948</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.434113603225207</v>
+        <v>9.434157966256663</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.358151101772696</v>
+        <v>9.358192520944449</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.290733466309259</v>
+        <v>9.290776973849665</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.267592562090206</v>
+        <v>9.267622985033411</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.280126041733451</v>
+        <v>9.280149581377668</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.238622805157586</v>
+        <v>9.238603723108429</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.168970451122304</v>
+        <v>9.168929944546495</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.104078026564554</v>
+        <v>9.104015363937387</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.009308955787599</v>
+        <v>9.009233505154983</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.937928619611789</v>
+        <v>8.937835731435481</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.93408925313847</v>
+        <v>8.933973582545327</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.943103961451531</v>
+        <v>8.942969100867138</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.066018681645247</v>
+        <v>9.065829722378485</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.119535936160744</v>
+        <v>9.119338367243666</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.286900742832248</v>
+        <v>9.286744183685741</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.381156641295675</v>
+        <v>9.381033707687948</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.400877781633103</v>
+        <v>9.400773054527413</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.485130179909927</v>
+        <v>9.485039627044939</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.60838257180392</v>
+        <v>9.608406067796714</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.601182116110333</v>
+        <v>9.601245205363531</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.621314749902186</v>
+        <v>9.621446917961119</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.622562790816584</v>
+        <v>9.622786530767941</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.604998220447154</v>
+        <v>9.6052555913436</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.641642423932009</v>
+        <v>9.641932856189545</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.507938074040595</v>
+        <v>9.508197800768745</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.439451496302413</v>
+        <v>9.43970012747997</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.28793866477281</v>
+        <v>9.288079578859461</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.189563631285754</v>
+        <v>9.189653711915316</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.075564586852577</v>
+        <v>9.075539236454031</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.047225283328771</v>
+        <v>9.047165227976128</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.044758074408465</v>
+        <v>9.044709842846652</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.018391364109178</v>
+        <v>9.018317072670065</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>8.998024170922733</v>
+        <v>8.997947830327039</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.010878744053944</v>
+        <v>9.010840666083723</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.039810611881176</v>
+        <v>9.039823132472405</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.060383302154033</v>
+        <v>9.060424395773797</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.060835263713006</v>
+        <v>9.060838286554489</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.047489967047305</v>
+        <v>9.047482711652739</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.038007028706167</v>
+        <v>9.037983108353405</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.0448200156089</v>
+        <v>9.044764144472172</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.059716150905992</v>
+        <v>9.059629931821112</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.070431899269131</v>
+        <v>9.070299526911731</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.085847778348924</v>
+        <v>9.085745120478286</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.070152636841716</v>
+        <v>9.070059752121949</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>9.055885728117126</v>
+        <v>9.055776101407623</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>9.038056643029513</v>
+        <v>9.037964567513013</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>9.017112848683443</v>
+        <v>9.017121647958962</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>8.993463366519263</v>
+        <v>8.993557177113143</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>8.982556444329099</v>
+        <v>8.979788351590766</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>8.976285642599763</v>
+        <v>8.973300631607566</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>8.964378479185276</v>
+        <v>8.961352692448266</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>8.956684276747481</v>
+        <v>8.952739161248253</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>8.939650559146056</v>
+        <v>8.935220972645819</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>8.917003119824802</v>
+        <v>8.911728626698119</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>8.884124541277508</v>
+        <v>8.878104029609927</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>8.821983797260355</v>
+        <v>8.8161386045693</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>8.766295086362963</v>
+        <v>8.760906398047606</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>8.702239367479761</v>
+        <v>8.696786362137946</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>8.613689183990296</v>
+        <v>8.61072539258913</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>8.549841818227815</v>
+        <v>8.548694520866595</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>8.50140665797975</v>
+        <v>8.500588525273624</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46395</v>
       </c>
       <c r="B120">
-        <v>8.550049716308807</v>
+        <v>8.49941644843231</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.748779106558217</v>
+        <v>9.748734817818921</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.724085003419583</v>
+        <v>9.723987605098589</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.721141657306918</v>
+        <v>9.72100728361545</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.700648676443132</v>
+        <v>9.700434933581757</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.705156937105929</v>
+        <v>9.704945388316169</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.6983989472154</v>
+        <v>9.698190060525672</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.694225051248919</v>
+        <v>9.694015182671224</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.708291630391315</v>
+        <v>9.708076610501715</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.720934382495539</v>
+        <v>9.720682275444979</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.727605979555808</v>
+        <v>9.727411325010522</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.7362650347082</v>
+        <v>9.736067980337978</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.712644818271201</v>
+        <v>9.712451839494792</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.668260731347321</v>
+        <v>9.668066844922443</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.634246013694433</v>
+        <v>9.634004023272011</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.600867491645326</v>
+        <v>9.600705560838428</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.56296569427621</v>
+        <v>9.562824677092559</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.505448434490948</v>
+        <v>9.50514168390279</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.434157966256663</v>
+        <v>9.43372982723468</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.358192520944449</v>
+        <v>9.357792763795278</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.290776973849665</v>
+        <v>9.2903571726088</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.267622985033411</v>
+        <v>9.267330097589456</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.280149581377668</v>
+        <v>9.279923453353023</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.238603723108429</v>
+        <v>9.23878884653349</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.168929944546495</v>
+        <v>9.169322078192426</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.104015363937387</v>
+        <v>9.104621618069455</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.009233505154983</v>
+        <v>9.009963356218822</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.937835731435481</v>
+        <v>8.938734087567097</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.933973582545327</v>
+        <v>8.935091935696443</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.942969100867138</v>
+        <v>8.944271407970021</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.065829722378485</v>
+        <v>9.067653606556632</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.119338367243666</v>
+        <v>9.121245314795086</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.286744183685741</v>
+        <v>9.288253634972554</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.381033707687948</v>
+        <v>9.382218452304055</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.400773054527413</v>
+        <v>9.401781094933536</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.485039627044939</v>
+        <v>9.485910023018398</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.608406067796714</v>
+        <v>9.608175799958893</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.601245205363531</v>
+        <v>9.600632009253575</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.621446917961119</v>
+        <v>9.620167505262998</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.622786530767941</v>
+        <v>9.620625681032163</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.6052555913436</v>
+        <v>9.60277076587019</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.641932856189545</v>
+        <v>9.639130025872028</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.508197800768745</v>
+        <v>9.505694153192023</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.43970012747997</v>
+        <v>9.437304944313748</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.288079578859461</v>
+        <v>9.286723728131468</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.189653711915316</v>
+        <v>9.188788014074646</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.075539236454031</v>
+        <v>9.075784980175712</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.047165227976128</v>
+        <v>9.047744370333884</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.044709842846652</v>
+        <v>9.045174699202954</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.018317072670065</v>
+        <v>9.019032003077756</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>8.997947830327039</v>
+        <v>8.998681475674779</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.010840666083723</v>
+        <v>9.011205519489231</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.039823132472405</v>
+        <v>9.039701148113181</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.060424395773797</v>
+        <v>9.060028634951333</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.060838286554489</v>
+        <v>9.060811691643689</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.047482711652739</v>
+        <v>9.05043978236934</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.037983108353405</v>
+        <v>9.039430951672271</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.044764144472172</v>
+        <v>9.044102925412473</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.059629931821112</v>
+        <v>9.053859390823815</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.070299526911731</v>
+        <v>9.062544390237672</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.085745120478286</v>
+        <v>9.079130855037608</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.070059752121949</v>
+        <v>9.063229278145009</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>9.055776101407623</v>
+        <v>9.049454991038967</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>9.037964567513013</v>
+        <v>9.035322733441596</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>9.017121647958962</v>
+        <v>9.020891792196604</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>8.993557177113143</v>
+        <v>8.998615658976332</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>8.979788351590766</v>
+        <v>8.973598506553419</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>8.973300631607566</v>
+        <v>8.962035452461958</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>8.961352692448266</v>
+        <v>8.939930890125369</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>8.952739161248253</v>
+        <v>8.918732570090393</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>8.935220972645819</v>
+        <v>8.903197563549362</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>8.911728626698119</v>
+        <v>8.889862154008373</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>8.878104029609927</v>
+        <v>8.869817099144665</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>8.8161386045693</v>
+        <v>8.81035141877198</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>8.760906398047606</v>
+        <v>8.753403792838736</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>8.696786362137946</v>
+        <v>8.69694432154802</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>8.61072539258913</v>
+        <v>8.624289052796941</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>8.548694520866595</v>
+        <v>8.592973199804801</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>8.500588525273624</v>
+        <v>8.598022014380456</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46395</v>
       </c>
       <c r="B120">
-        <v>8.49941644843231</v>
+        <v>8.586593752135521</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.748734817818921</v>
+        <v>9.748788053841768</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.723987605098589</v>
+        <v>9.724104680956795</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.72100728361545</v>
+        <v>9.721168808879893</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.700434933581757</v>
+        <v>9.700691860668416</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.704945388316169</v>
+        <v>9.705199677380707</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.698190060525672</v>
+        <v>9.698441149382848</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.694015182671224</v>
+        <v>9.694267449740485</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.708076610501715</v>
+        <v>9.708335064649111</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.720682275444979</v>
+        <v>9.72098532131217</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.727411325010522</v>
+        <v>9.727645314899814</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.736067980337978</v>
+        <v>9.736304855015554</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.712451839494792</v>
+        <v>9.712683815588152</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.668066844922443</v>
+        <v>9.668299929645359</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.634004023272011</v>
+        <v>9.63429493783376</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.600705560838428</v>
+        <v>9.600900240344767</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.562824677092559</v>
+        <v>9.562994193628032</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.50514168390279</v>
+        <v>9.505510410091023</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.43372982723468</v>
+        <v>9.434244503830989</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.357792763795278</v>
+        <v>9.358273314052472</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.2903571726088</v>
+        <v>9.290861848298874</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.267330097589456</v>
+        <v>9.267682379607866</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.279923453353023</v>
+        <v>9.280195571653978</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.23878884653349</v>
+        <v>9.238566566957809</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.169322078192426</v>
+        <v>9.168851013264437</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.104621618069455</v>
+        <v>9.10389323404925</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.009963356218822</v>
+        <v>9.00908644275658</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.938734087567097</v>
+        <v>8.937654669342443</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.935091935696443</v>
+        <v>8.933748088514895</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.944271407970021</v>
+        <v>8.942706087520444</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.067653606556632</v>
+        <v>9.06546114485308</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.121245314795086</v>
+        <v>9.118952993334201</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.288253634972554</v>
+        <v>9.286438687781411</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.382218452304055</v>
+        <v>9.380793790749069</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.401781094933536</v>
+        <v>9.400568583828857</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.485910023018398</v>
+        <v>9.484862746938864</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.608175799958893</v>
+        <v>9.608451658608612</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.600632009253575</v>
+        <v>9.601367972663464</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.620167505262998</v>
+        <v>9.621704465707218</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.620625681032163</v>
+        <v>9.623222863703356</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.60277076587019</v>
+        <v>9.605757567358069</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.639130025872028</v>
+        <v>9.642499397503865</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.505694153192023</v>
+        <v>9.508704642401042</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.437304944313748</v>
+        <v>9.440185420614505</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.286723728131468</v>
+        <v>9.288354736584331</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.188788014074646</v>
+        <v>9.189829681216802</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.075784980175712</v>
+        <v>9.075489861942946</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.047744370333884</v>
+        <v>9.047048050054951</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.045174699202954</v>
+        <v>9.04461571703073</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.019032003077756</v>
+        <v>9.018172014282529</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>8.998681475674779</v>
+        <v>8.997798701303402</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.011205519489231</v>
+        <v>9.010766207116777</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.039701148113181</v>
+        <v>9.039847476415515</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.060028634951333</v>
+        <v>9.060504612393331</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.060811691643689</v>
+        <v>9.060844361020887</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.05043978236934</v>
+        <v>9.04746864173832</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.039430951672271</v>
+        <v>9.037936463841859</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.044102925412473</v>
+        <v>9.044655050971873</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.053859390823815</v>
+        <v>9.05946146031965</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.062544390237672</v>
+        <v>9.070040795294801</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.079130855037608</v>
+        <v>9.085544588858802</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.063229278145009</v>
+        <v>9.069878098204811</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>9.049454991038967</v>
+        <v>9.055561512749243</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>9.035322733441596</v>
+        <v>9.037783755059275</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>9.020891792196604</v>
+        <v>9.017137433363953</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>8.998615658976332</v>
+        <v>8.993738816947143</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>8.973598506553419</v>
+        <v>8.975017488812384</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>8.962035452461958</v>
+        <v>8.968343319809222</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>8.939930890125369</v>
+        <v>8.956523058983198</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>8.918732570090393</v>
+        <v>8.946228112727503</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>8.903197563549362</v>
+        <v>8.928046918076998</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>8.889862154008373</v>
+        <v>8.903114229853863</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>8.869817099144665</v>
+        <v>8.868286068061888</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>8.81035141877198</v>
+        <v>8.80690564743928</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>8.753403792838736</v>
+        <v>8.752896488730858</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>8.69694432154802</v>
+        <v>8.689447470228476</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>8.624289052796941</v>
+        <v>8.608632942337023</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>8.592973199804801</v>
+        <v>8.550716778486702</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>8.598022014380456</v>
+        <v>8.505501822406247</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46395</v>
       </c>
       <c r="B120">
-        <v>8.586593752135521</v>
+        <v>8.488796736073336</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.748788053841768</v>
+        <v>9.748740093426306</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.724104680956795</v>
+        <v>9.72399920661822</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.721168808879893</v>
+        <v>9.72102328776141</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.700691860668416</v>
+        <v>9.700460392761022</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.705199677380707</v>
+        <v>9.70497058644372</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.698441149382848</v>
+        <v>9.698214941679977</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.694267449740485</v>
+        <v>9.69404018166718</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.708335064649111</v>
+        <v>9.708102225235425</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.72098532131217</v>
+        <v>9.720712302676251</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.727645314899814</v>
+        <v>9.72743450723029</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.736304855015554</v>
+        <v>9.736091448357435</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.712683815588152</v>
+        <v>9.712474821877311</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.668299929645359</v>
+        <v>9.66808992780353</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.63429493783376</v>
+        <v>9.634032832849147</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.600900240344767</v>
+        <v>9.600724834570542</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.562994193628032</v>
+        <v>9.562841470148816</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.505510410091023</v>
+        <v>9.505178221195353</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.434244503830989</v>
+        <v>9.43378080725835</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.358273314052472</v>
+        <v>9.357840367664581</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.290861848298874</v>
+        <v>9.290407150305636</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.267682379607866</v>
+        <v>9.267364888607977</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.280195571653978</v>
+        <v>9.279950256453816</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.238566566957809</v>
+        <v>9.238766690148113</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.168851013264437</v>
+        <v>9.169275243598939</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.10389323404925</v>
+        <v>9.104549252728004</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.00908644275658</v>
+        <v>9.009876252499756</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.937654669342443</v>
+        <v>8.93862689386771</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.933748088514895</v>
+        <v>8.934958531336438</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.942706087520444</v>
+        <v>8.944116245055625</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.06546114485308</v>
+        <v>9.067436398545896</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.118952993334201</v>
+        <v>9.121018219293466</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.286438687781411</v>
+        <v>9.288074071941566</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.380793790749069</v>
+        <v>9.382077575834089</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.400568583828857</v>
+        <v>9.40166137601963</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.484862746938864</v>
+        <v>9.485806793624928</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.608451658608612</v>
+        <v>9.608203629889797</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.601367972663464</v>
+        <v>9.600705531686199</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.621704465707218</v>
+        <v>9.620320303395458</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.623222863703356</v>
+        <v>9.620883164989321</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.605757567358069</v>
+        <v>9.603066757251128</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.642499397503865</v>
+        <v>9.639463758915845</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.508704642401042</v>
+        <v>9.505991928217229</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.440185420614505</v>
+        <v>9.437589642071526</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.288354736584331</v>
+        <v>9.286884695609718</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.189829681216802</v>
+        <v>9.188890668320258</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.075489861942946</v>
+        <v>9.075755591304198</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.047048050054951</v>
+        <v>9.047675461896283</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.04461571703073</v>
+        <v>9.045119419904093</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.018172014282529</v>
+        <v>9.018947113131606</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>8.997798701303402</v>
+        <v>8.99859448115831</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.010766207116777</v>
+        <v>9.011162382651703</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.039847476415515</v>
+        <v>9.039715807574506</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.060504612393331</v>
+        <v>9.060075662582891</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.060844361020887</v>
+        <v>9.060814556918126</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.04746864173832</v>
+        <v>9.05042435995203</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.037936463841859</v>
+        <v>9.039400326111886</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.044655050971873</v>
+        <v>9.044039803728765</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.05946146031965</v>
+        <v>9.05376844654981</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.070040795294801</v>
+        <v>9.062402442823959</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.085544588858802</v>
+        <v>9.079024551258289</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.069878098204811</v>
+        <v>9.063128215908449</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>9.055561512749243</v>
+        <v>9.0493314807229</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>9.037783755059275</v>
+        <v>9.035210621120523</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>9.017137433363953</v>
+        <v>9.020880251588583</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>8.993738816947143</v>
+        <v>8.998694203836481</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>8.975017488812384</v>
+        <v>8.970849263549304</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>8.968343319809222</v>
+        <v>8.959267462140833</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>8.956523058983198</v>
+        <v>8.93771774044594</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>8.946228112727503</v>
+        <v>8.916401721969354</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>8.928046918076998</v>
+        <v>8.900329219787672</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>8.903114229853863</v>
+        <v>8.886306353143983</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>8.868286068061888</v>
+        <v>8.865702740462005</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>8.80690564743928</v>
+        <v>8.806878939042885</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>8.752896488730858</v>
+        <v>8.750957538161671</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>8.689447470228476</v>
+        <v>8.69542833349195</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>8.608632942337023</v>
+        <v>8.625513709819579</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>8.550716778486702</v>
+        <v>8.595677816469223</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>8.505501822406247</v>
+        <v>8.598540476711552</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46395</v>
       </c>
       <c r="B120">
-        <v>8.488796736073336</v>
+        <v>8.583386907105295</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.748740093426306</v>
+        <v>9.748792417483429</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.72399920661822</v>
+        <v>9.724114277922492</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.72102328776141</v>
+        <v>9.721182051487935</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.700460392761022</v>
+        <v>9.700712922290478</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.70497058644372</v>
+        <v>9.705220522400136</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.698214941679977</v>
+        <v>9.698461731927001</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.69404018166718</v>
+        <v>9.694288127784391</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.708102225235425</v>
+        <v>9.708356247243252</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.720712302676251</v>
+        <v>9.721010165398091</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.72743450723029</v>
+        <v>9.727664500298236</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.736091448357435</v>
+        <v>9.736324276951159</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.712474821877311</v>
+        <v>9.712702836191617</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.66808992780353</v>
+        <v>9.668319050414294</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.634032832849147</v>
+        <v>9.634318802897774</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.600724834570542</v>
+        <v>9.60091621635576</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.562841470148816</v>
+        <v>9.563008094240736</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.505178221195353</v>
+        <v>9.505540636578326</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.43378080725835</v>
+        <v>9.434286714051449</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.357840367664581</v>
+        <v>9.358312721364532</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.290407150305636</v>
+        <v>9.290903250018181</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.267364888607977</v>
+        <v>9.267711374091398</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.279950256453816</v>
+        <v>9.280218038861449</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.238766690148113</v>
+        <v>9.238548475344531</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.169275243598939</v>
+        <v>9.168812553270314</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.104549252728004</v>
+        <v>9.103833713024141</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.009876252499756</v>
+        <v>9.009014766543874</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.93862689386771</v>
+        <v>8.937566416477752</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.934958531336438</v>
+        <v>8.933638167540931</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.944116245055625</v>
+        <v>8.942577824554547</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.067436398545896</v>
+        <v>9.065281374070615</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.121018219293466</v>
+        <v>9.11876502895775</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.288074071941566</v>
+        <v>9.286289628475064</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.382077575834089</v>
+        <v>9.380676712343501</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.40166137601963</v>
+        <v>9.400468762050142</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.485806793624928</v>
+        <v>9.484776354825712</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.608203629889797</v>
+        <v>9.608473780201052</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.600705531686199</v>
+        <v>9.601427711137266</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.620320303395458</v>
+        <v>9.621829960316255</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.620883164989321</v>
+        <v>9.623435640066036</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.603066757251128</v>
+        <v>9.60600238152499</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.639463758915845</v>
+        <v>9.642775739839458</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.505991928217229</v>
+        <v>9.508951959529764</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.437589642071526</v>
+        <v>9.4404222727575</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.286884695609718</v>
+        <v>9.288489084335428</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.188890668320258</v>
+        <v>9.189915634152307</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.075755591304198</v>
+        <v>9.075465815053626</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.047675461896283</v>
+        <v>9.04699088024201</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.045119419904093</v>
+        <v>9.044569785437661</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.018947113131606</v>
+        <v>9.018101192208011</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>8.99859448115831</v>
+        <v>8.99772585844469</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.011162382651703</v>
+        <v>9.010729801365557</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.039715807574506</v>
+        <v>9.039859312380216</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.060075662582891</v>
+        <v>9.060543766547493</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.060814556918126</v>
+        <v>9.060847409324829</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.05042435995203</v>
+        <v>9.047461818873494</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.039400326111886</v>
+        <v>9.037913720133824</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.044039803728765</v>
+        <v>9.044601787422739</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.05376844654981</v>
+        <v>9.059379148128045</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.062402442823959</v>
+        <v>9.069914346609362</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.079024551258289</v>
+        <v>9.085446642184632</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.063128215908449</v>
+        <v>9.069789270232906</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>9.0493314807229</v>
+        <v>9.05545648766444</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>9.035210621120523</v>
+        <v>9.037694983688752</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>9.020880251588583</v>
+        <v>9.01714447041654</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>8.998694203836481</v>
+        <v>8.993826762625062</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>8.970849263549304</v>
+        <v>8.972563603996957</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>8.959267462140833</v>
+        <v>8.965711178738808</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>8.93771774044594</v>
+        <v>8.953932867980939</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>8.916401721969354</v>
+        <v>8.942693780466762</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>8.900329219787672</v>
+        <v>8.924233702906218</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>8.886306353143983</v>
+        <v>8.898597501465826</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>8.865702740462005</v>
+        <v>8.86318292814267</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>8.806878939042885</v>
+        <v>8.802040124337349</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>8.750957538161671</v>
+        <v>8.748530382103844</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>8.69542833349195</v>
+        <v>8.685230514616986</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>8.625513709819579</v>
+        <v>8.606502289454557</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>8.595677816469223</v>
+        <v>8.549948189876055</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>8.598540476711552</v>
+        <v>8.504851658084984</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46395</v>
       </c>
       <c r="B120">
-        <v>8.583386907105295</v>
+        <v>8.481424660359572</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>8.965711178738808</v>
+        <v>8.965711503046435</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>8.953932867980939</v>
+        <v>8.953947026617108</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>8.942693780466762</v>
+        <v>8.943013470127344</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>8.924233702906218</v>
+        <v>8.924259577809629</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>8.898597501465826</v>
+        <v>8.898623792091541</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>8.86318292814267</v>
+        <v>8.86321009650684</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>8.802040124337349</v>
+        <v>8.802070951080399</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>8.748530382103844</v>
+        <v>8.748572075490987</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>8.685230514616986</v>
+        <v>8.685299123746571</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>8.606502289454557</v>
+        <v>8.606598379567536</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>8.549948189876055</v>
+        <v>8.550079490010017</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>8.504851658084984</v>
+        <v>8.505051058657001</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46395</v>
       </c>
       <c r="B120">
-        <v>8.481424660359572</v>
+        <v>8.481843061197718</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B120"/>
+  <dimension ref="A1:B121"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.748792417483429</v>
+        <v>9.748745274833995</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.724114277922492</v>
+        <v>9.724010601095541</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.721182051487935</v>
+        <v>9.721039006733903</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.700712922290478</v>
+        <v>9.700485397758397</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.705220522400136</v>
+        <v>9.704995334970929</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.698461731927001</v>
+        <v>9.698239378858945</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.694288127784391</v>
+        <v>9.694064734351858</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.708356247243252</v>
+        <v>9.708127382105067</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.721010165398091</v>
+        <v>9.720741794645678</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.727664500298236</v>
+        <v>9.727457276764763</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.736324276951159</v>
+        <v>9.736114498605311</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.712702836191617</v>
+        <v>9.712497395201245</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.668319050414294</v>
+        <v>9.668112601838619</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.634318802897774</v>
+        <v>9.634061132217809</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.60091621635576</v>
+        <v>9.600743768167167</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.563008094240736</v>
+        <v>9.562857964592729</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.505540636578326</v>
+        <v>9.505214106724711</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.434286714051449</v>
+        <v>9.433830882089502</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.358312721364532</v>
+        <v>9.357887125396511</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.290903250018181</v>
+        <v>9.290456243103879</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.267711374091398</v>
+        <v>9.267399084034178</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.280218038861449</v>
+        <v>9.279976615967655</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.238548475344531</v>
+        <v>9.2387449569331</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.168812553270314</v>
+        <v>9.169229277917513</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.103833713024141</v>
+        <v>9.104478218726936</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.009014766543874</v>
+        <v>9.00979074738478</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.937566416477752</v>
+        <v>8.938521662166892</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.933638167540931</v>
+        <v>8.934827558226416</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.942577824554547</v>
+        <v>8.943963861491591</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.065281374070615</v>
+        <v>9.067223055458124</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.11876502895775</v>
+        <v>9.120795163435414</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.286289628475064</v>
+        <v>9.287897651616886</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.380676712343501</v>
+        <v>9.381939149214109</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.400468762050142</v>
+        <v>9.40154370052587</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.484776354825712</v>
+        <v>9.485705288608976</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.608473780201052</v>
+        <v>9.608230857455071</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.601427711137266</v>
+        <v>9.600777615272552</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.621829960316255</v>
+        <v>9.620470269156298</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.623435640066036</v>
+        <v>9.621136028898345</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.60600238152499</v>
+        <v>9.603357463267567</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.642775739839458</v>
+        <v>9.639791569118954</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.508951959529764</v>
+        <v>9.506284506527713</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.4404222727575</v>
+        <v>9.437869417990939</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.288489084335428</v>
+        <v>9.28704293104019</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.189915634152307</v>
+        <v>9.188991612347989</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.075465815053626</v>
+        <v>9.075726757635042</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.04699088024201</v>
+        <v>9.047607763129296</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.044569785437661</v>
+        <v>9.045065102830565</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.018101192208011</v>
+        <v>9.018863667384823</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>8.99772585844469</v>
+        <v>8.9985089356794</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.010729801365557</v>
+        <v>9.011119930853162</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.039859312380216</v>
+        <v>9.039730171459858</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.060543766547493</v>
+        <v>9.060121880827282</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.060847409324829</v>
+        <v>9.060817450607711</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.047461818873494</v>
+        <v>9.050409263007335</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.037913720133824</v>
+        <v>9.039370255860305</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.044601787422739</v>
+        <v>9.043977758247506</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.059379148128045</v>
+        <v>9.05367900118399</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.069914346609362</v>
+        <v>9.062262814196041</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.085446642184632</v>
+        <v>9.078920044489591</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.069789270232906</v>
+        <v>9.063028824868692</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>9.05545648766444</v>
+        <v>9.049209948341176</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>9.037694983688752</v>
+        <v>9.035100100901342</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>9.01714447041654</v>
+        <v>9.020868440864605</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>8.993826762625062</v>
+        <v>8.998770871270461</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>8.972563603996957</v>
+        <v>8.970991964122373</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>8.965711503046435</v>
+        <v>8.956499367522193</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>8.953947026617108</v>
+        <v>8.934810859734627</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>8.943013470127344</v>
+        <v>8.914078773523617</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>8.924259577809629</v>
+        <v>8.897432689859496</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>8.898623792091541</v>
+        <v>8.88271962008039</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>8.86321009650684</v>
+        <v>8.861695032933666</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>8.802070951080399</v>
+        <v>8.803797592871678</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>8.748572075490987</v>
+        <v>8.749274879815232</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>8.685299123746571</v>
+        <v>8.695653848750029</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>8.606598379567536</v>
+        <v>8.62803367338636</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>8.550079490010017</v>
+        <v>8.600258828309292</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>8.505051058657001</v>
+        <v>8.603192340991784</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,15 @@
         <v>46395</v>
       </c>
       <c r="B120">
-        <v>8.481843061197718</v>
+        <v>8.591196946626432</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121" s="3">
+        <v>46402</v>
+      </c>
+      <c r="B121">
+        <v>8.629002490710191</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.748745274833995</v>
+        <v>9.748796710176299</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.724010601095541</v>
+        <v>9.724123718925476</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.721039006733903</v>
+        <v>9.721195079185824</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.700485397758397</v>
+        <v>9.700733641742101</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.704995334970929</v>
+        <v>9.70524102871625</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.698239378858945</v>
+        <v>9.698481980011618</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.694064734351858</v>
+        <v>9.694308469656944</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.708127382105067</v>
+        <v>9.70837708507934</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.720741794645678</v>
+        <v>9.721034606136016</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.727457276764763</v>
+        <v>9.727683374606116</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.736114498605311</v>
+        <v>9.736343383961685</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.712497395201245</v>
+        <v>9.712721548424128</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.668112601838619</v>
+        <v>9.66833786255599</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.634061132217809</v>
+        <v>9.634342282801315</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.600743768167167</v>
+        <v>9.60093193534939</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.562857964592729</v>
+        <v>9.563021769682317</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.505214106724711</v>
+        <v>9.505570372010069</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.433830882089502</v>
+        <v>9.434328241384716</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.357887125396511</v>
+        <v>9.358351490532439</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.290456243103879</v>
+        <v>9.290943983672072</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.267399084034178</v>
+        <v>9.267739914680165</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.279976615967655</v>
+        <v>9.280240164750634</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.2387449569331</v>
+        <v>9.238530696865435</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.169229277917513</v>
+        <v>9.168774741168782</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.104478218726936</v>
+        <v>9.103775186928312</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.00979074738478</v>
+        <v>9.008944285809536</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.938521662166892</v>
+        <v>8.937479631950659</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.934827558226416</v>
+        <v>8.933530068254962</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.943963861491591</v>
+        <v>8.942451653581681</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.067223055458124</v>
+        <v>9.06510451770588</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.120795163435414</v>
+        <v>9.118580111007976</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.287897651616886</v>
+        <v>9.28614294982021</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.381939149214109</v>
+        <v>9.380561493105013</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.40154370052587</v>
+        <v>9.400370499216425</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.485705288608976</v>
+        <v>9.484691286395122</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.608230857455071</v>
+        <v>9.60849546960665</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.600777615272552</v>
+        <v>9.601486391355614</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.620470269156298</v>
+        <v>9.621953342156548</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.621136028898345</v>
+        <v>9.623644940296568</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.603357463267567</v>
+        <v>9.606243213512657</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.639791569118954</v>
+        <v>9.643047612539036</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.506284506527713</v>
+        <v>9.509195336995951</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.437869417990939</v>
+        <v>9.440655383754322</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.28704293104019</v>
+        <v>9.288621344742236</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.188991612347989</v>
+        <v>9.1900002738311</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.075726757635042</v>
+        <v>9.075442180533212</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.047607763129296</v>
+        <v>9.046934626286564</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.045065102830565</v>
+        <v>9.044524584145076</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.018863667384823</v>
+        <v>9.018031472883422</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>8.9985089356794</v>
+        <v>8.997654128440399</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.011119930853162</v>
+        <v>9.010693928855932</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.039730171459858</v>
+        <v>9.039870932376903</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.060121880827282</v>
+        <v>9.060582304555691</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.060817450607711</v>
+        <v>9.060850462960133</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.050409263007335</v>
+        <v>9.047455132091049</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.039370255860305</v>
+        <v>9.037891349613865</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.043977758247506</v>
+        <v>9.044549352933789</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.05367900118399</v>
+        <v>9.059298079933249</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.062262814196041</v>
+        <v>9.06978978523046</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.078920044489591</v>
+        <v>9.085350194800249</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.063028824868692</v>
+        <v>9.069701737079621</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>9.049209948341176</v>
+        <v>9.055352934657884</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>9.035100100901342</v>
+        <v>9.037607279658449</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>9.020868440864605</v>
+        <v>9.017150969081381</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>8.998770871270461</v>
+        <v>8.99391286622062</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>8.970991964122373</v>
+        <v>8.972696100860528</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>8.956499367522193</v>
+        <v>8.963126948029817</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>8.934810859734627</v>
+        <v>8.951225366143689</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>8.914078773523617</v>
+        <v>8.940190730241724</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>8.897432689859496</v>
+        <v>8.920628050220436</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>8.88271962008039</v>
+        <v>8.894767541761102</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>8.861695032933666</v>
+        <v>8.859301871593331</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>8.803797592871678</v>
+        <v>8.798932151887982</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>8.749274879815232</v>
+        <v>8.746563170249667</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>8.695653848750029</v>
+        <v>8.685372434534642</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>8.62803367338636</v>
+        <v>8.609283231672048</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>8.600258828309292</v>
+        <v>8.556066690514999</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>8.603192340991784</v>
+        <v>8.515293262787786</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46395</v>
       </c>
       <c r="B120">
-        <v>8.591196946626432</v>
+        <v>8.499892989137933</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -1354,7 +1354,7 @@
         <v>46402</v>
       </c>
       <c r="B121">
-        <v>8.629002490710191</v>
+        <v>8.564878626722088</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.748796710176299</v>
+        <v>9.748750364542598</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.724123718925476</v>
+        <v>9.724021794023605</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.721195079185824</v>
+        <v>9.721054448087052</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.700733641742101</v>
+        <v>9.700509960618517</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.70524102871625</v>
+        <v>9.705019645822917</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.698481980011618</v>
+        <v>9.698263383839294</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.694308469656944</v>
+        <v>9.694088852570063</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.70837708507934</v>
+        <v>9.708152093276778</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.721034606136016</v>
+        <v>9.720770765535866</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.727683374606116</v>
+        <v>9.727479644534663</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.736343383961685</v>
+        <v>9.736137142136876</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.712721548424128</v>
+        <v>9.712519570289512</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.66833786255599</v>
+        <v>9.668134877791596</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.634342282801315</v>
+        <v>9.634088934808219</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.60093193534939</v>
+        <v>9.600762370550196</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.563021769682317</v>
+        <v>9.562874168317206</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.505570372010069</v>
+        <v>9.505249357770605</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.434328241384716</v>
+        <v>9.433880075612148</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.358351490532439</v>
+        <v>9.357933059341519</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.290943983672072</v>
+        <v>9.290504474290303</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.267739914680165</v>
+        <v>9.267432698997972</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.280240164750634</v>
+        <v>9.280002542745354</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.238530696865435</v>
+        <v>9.238723634942021</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.168774741168782</v>
+        <v>9.169184157248065</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.103775186928312</v>
+        <v>9.104408479732797</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.008944285809536</v>
+        <v>9.009706797352539</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.937479631950659</v>
+        <v>8.938418339192246</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.933530068254962</v>
+        <v>8.934698950631889</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.942451653581681</v>
+        <v>8.943814183337743</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.06510451770588</v>
+        <v>9.067013475155319</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.118580111007976</v>
+        <v>9.120576040498751</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.28614294982021</v>
+        <v>9.287724292333598</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.380561493105013</v>
+        <v>9.38180310921561</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.400370499216425</v>
+        <v>9.40142801676642</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.484691286395122</v>
+        <v>9.485605465397004</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.60849546960665</v>
+        <v>9.608257501391535</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.601486391355614</v>
+        <v>9.600848301452128</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.621953342156548</v>
+        <v>9.620617480333834</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.623644940296568</v>
+        <v>9.621384395832479</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.606243213512657</v>
+        <v>9.603643024011642</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.643047612539036</v>
+        <v>9.640113612562516</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.509195336995951</v>
+        <v>9.506572022772234</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.440655383754322</v>
+        <v>9.438144398334558</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.288621344742236</v>
+        <v>9.28719850314504</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.1900002738311</v>
+        <v>9.18909088833913</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.075442180533212</v>
+        <v>9.075698463700045</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.046934626286564</v>
+        <v>9.047541242543311</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.044524584145076</v>
+        <v>9.045011723164579</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.018031472883422</v>
+        <v>9.018781629428599</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>8.997654128440399</v>
+        <v>8.998424803520685</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.010693928855932</v>
+        <v>9.011078148114848</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.039870932376903</v>
+        <v>9.039744248459174</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.060582304555691</v>
+        <v>9.060167310326523</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.060850462960133</v>
+        <v>9.060820369909973</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.047455132091049</v>
+        <v>9.050394481721479</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.037891349613865</v>
+        <v>9.039340726131119</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.044549352933789</v>
+        <v>9.043916761935698</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.059298079933249</v>
+        <v>9.053591018384726</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.06978978523046</v>
+        <v>9.06212544858866</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.085350194800249</v>
+        <v>9.078817289927382</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.069701737079621</v>
+        <v>9.062931064540955</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>9.055352934657884</v>
+        <v>9.049090347880888</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>9.037607279658449</v>
+        <v>9.034991141673263</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>9.017150969081381</v>
+        <v>9.020856379379245</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>8.99391286622062</v>
+        <v>8.998845722288802</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>8.972696100860528</v>
+        <v>8.971131782847774</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>8.963126948029817</v>
+        <v>8.954561286193039</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>8.951225366143689</v>
+        <v>8.932975105715439</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>8.940190730241724</v>
+        <v>8.912882523906363</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>8.920628050220436</v>
+        <v>8.89608940412784</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>8.894767541761102</v>
+        <v>8.880864105963703</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>8.859301871593331</v>
+        <v>8.859552789134796</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>8.798932151887982</v>
+        <v>8.802759836625848</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>8.746563170249667</v>
+        <v>8.749877984686631</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>8.685372434534642</v>
+        <v>8.69846777432978</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>8.609283231672048</v>
+        <v>8.633663071467854</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>8.556066690514999</v>
+        <v>8.608618307382789</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>8.515293262787786</v>
+        <v>8.613119935273607</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46395</v>
       </c>
       <c r="B120">
-        <v>8.499892989137933</v>
+        <v>8.606992441071043</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -1354,7 +1354,7 @@
         <v>46402</v>
       </c>
       <c r="B121">
-        <v>8.564878626722088</v>
+        <v>8.664704936629182</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B121"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -399,114 +399,962 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="3">
-        <v>46304</v>
+        <v>44743</v>
       </c>
       <c r="B2">
-        <v>8.861319999999999</v>
+        <v>8.245109090909091</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="3">
-        <v>46311</v>
+        <v>44778</v>
       </c>
       <c r="B3">
-        <v>8.853650343779517</v>
+        <v>8.236811339693453</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="3">
-        <v>46318</v>
+        <v>44806</v>
       </c>
       <c r="B4">
-        <v>8.847142031223626</v>
+        <v>8.200917545032613</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="3">
-        <v>46325</v>
+        <v>44834</v>
       </c>
       <c r="B5">
-        <v>8.817901907883032</v>
+        <v>8.041181403389656</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="3">
-        <v>46332</v>
+        <v>44869</v>
       </c>
       <c r="B6">
-        <v>8.78375050864409</v>
+        <v>8.036444362639676</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="3">
-        <v>46339</v>
+        <v>44897</v>
       </c>
       <c r="B7">
-        <v>8.740045623493629</v>
+        <v>8.023593201690472</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="3">
-        <v>46346</v>
+        <v>44932</v>
       </c>
       <c r="B8">
-        <v>8.695744942523161</v>
+        <v>8.196654104488639</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="3">
-        <v>46353</v>
+        <v>44960</v>
       </c>
       <c r="B9">
-        <v>8.659287121095922</v>
+        <v>8.176695138990606</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="3">
-        <v>46360</v>
+        <v>44988</v>
       </c>
       <c r="B10">
-        <v>8.640793586684563</v>
+        <v>8.139102610085022</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="3">
-        <v>46367</v>
+        <v>45016</v>
       </c>
       <c r="B11">
-        <v>8.614628178905189</v>
+        <v>8.155601354862256</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="3">
-        <v>46374</v>
+        <v>45051</v>
       </c>
       <c r="B12">
-        <v>8.598666117079988</v>
+        <v>8.365283790368187</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="3">
-        <v>46381</v>
+        <v>45079</v>
       </c>
       <c r="B13">
-        <v>8.574276384461287</v>
+        <v>8.383012221157303</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="3">
-        <v>46388</v>
+        <v>45107</v>
       </c>
       <c r="B14">
-        <v>8.534570881985228</v>
+        <v>8.604027516651747</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="3">
+        <v>45142</v>
+      </c>
+      <c r="B15">
+        <v>8.647073242959834</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="3">
+        <v>45170</v>
+      </c>
+      <c r="B16">
+        <v>8.591181327847133</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="3">
+        <v>45205</v>
+      </c>
+      <c r="B17">
+        <v>8.684484107738795</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="3">
+        <v>45233</v>
+      </c>
+      <c r="B18">
+        <v>8.908236983217812</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="3">
+        <v>45261</v>
+      </c>
+      <c r="B19">
+        <v>8.926735952446251</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="3">
+        <v>45296</v>
+      </c>
+      <c r="B20">
+        <v>8.981892481196068</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="3">
+        <v>45324</v>
+      </c>
+      <c r="B21">
+        <v>8.934405333835194</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="3">
+        <v>45352</v>
+      </c>
+      <c r="B22">
+        <v>9.014394774068943</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="3">
+        <v>45387</v>
+      </c>
+      <c r="B23">
+        <v>8.993456401987711</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="3">
+        <v>45415</v>
+      </c>
+      <c r="B24">
+        <v>9.105334481633466</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="3">
+        <v>45443</v>
+      </c>
+      <c r="B25">
+        <v>9.123841096414056</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="3">
+        <v>45478</v>
+      </c>
+      <c r="B26">
+        <v>9.193421582962779</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="3">
+        <v>45506</v>
+      </c>
+      <c r="B27">
+        <v>9.286259831755583</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" s="3">
+        <v>45541</v>
+      </c>
+      <c r="B28">
+        <v>9.322464567524264</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" s="3">
+        <v>45569</v>
+      </c>
+      <c r="B29">
+        <v>9.319892611634614</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" s="3">
+        <v>45597</v>
+      </c>
+      <c r="B30">
+        <v>9.231399536132812</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" s="3">
+        <v>45632</v>
+      </c>
+      <c r="B31">
+        <v>9.185700416564941</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" s="3">
+        <v>45660</v>
+      </c>
+      <c r="B32">
+        <v>9.117313385009766</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="3">
+        <v>45688</v>
+      </c>
+      <c r="B33">
+        <v>9.141136888817321</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" s="3">
+        <v>45716</v>
+      </c>
+      <c r="B34">
+        <v>9.099170017242431</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" s="3">
+        <v>45751</v>
+      </c>
+      <c r="B35">
+        <v>9.290665223789381</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" s="3">
+        <v>45779</v>
+      </c>
+      <c r="B36">
+        <v>9.583</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" s="3">
+        <v>45814</v>
+      </c>
+      <c r="B37">
+        <v>9.733499999999999</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" s="3">
+        <v>45821</v>
+      </c>
+      <c r="B38">
+        <v>9.815633405796371</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" s="3">
+        <v>45828</v>
+      </c>
+      <c r="B39">
+        <v>9.811192638312095</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" s="3">
+        <v>45835</v>
+      </c>
+      <c r="B40">
+        <v>9.800489278448216</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" s="3">
+        <v>45842</v>
+      </c>
+      <c r="B41">
+        <v>9.799573879005699</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" s="3">
+        <v>45849</v>
+      </c>
+      <c r="B42">
+        <v>9.748755364965</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" s="3">
+        <v>45856</v>
+      </c>
+      <c r="B43">
+        <v>9.724032790702863</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" s="3">
+        <v>45863</v>
+      </c>
+      <c r="B44">
+        <v>9.72106961911053</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" s="3">
+        <v>45870</v>
+      </c>
+      <c r="B45">
+        <v>9.70053409296391</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" s="3">
+        <v>45877</v>
+      </c>
+      <c r="B46">
+        <v>9.705043530506806</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" s="3">
+        <v>45884</v>
+      </c>
+      <c r="B47">
+        <v>9.698286967984922</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" s="3">
+        <v>45891</v>
+      </c>
+      <c r="B48">
+        <v>9.694112547751192</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" s="3">
+        <v>45898</v>
+      </c>
+      <c r="B49">
+        <v>9.708176370489511</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" s="3">
+        <v>45905</v>
+      </c>
+      <c r="B50">
+        <v>9.720799229032862</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" s="3">
+        <v>45912</v>
+      </c>
+      <c r="B51">
+        <v>9.727501621078833</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" s="3">
+        <v>45919</v>
+      </c>
+      <c r="B52">
+        <v>9.736159389620813</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" s="3">
+        <v>45926</v>
+      </c>
+      <c r="B53">
+        <v>9.712541357586636</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" s="3">
+        <v>45933</v>
+      </c>
+      <c r="B54">
+        <v>9.668156766051903</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" s="3">
+        <v>45940</v>
+      </c>
+      <c r="B55">
+        <v>9.63411625358348</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" s="3">
+        <v>45947</v>
+      </c>
+      <c r="B56">
+        <v>9.600780650332322</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" s="3">
+        <v>45954</v>
+      </c>
+      <c r="B57">
+        <v>9.562890088939477</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" s="3">
+        <v>45961</v>
+      </c>
+      <c r="B58">
+        <v>9.505283991007499</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" s="3">
+        <v>45968</v>
+      </c>
+      <c r="B59">
+        <v>9.433928410877803</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" s="3">
+        <v>45975</v>
+      </c>
+      <c r="B60">
+        <v>9.357978191070117</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" s="3">
+        <v>45982</v>
+      </c>
+      <c r="B61">
+        <v>9.290551866342017</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" s="3">
+        <v>45989</v>
+      </c>
+      <c r="B62">
+        <v>9.267465748122341</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63" s="3">
+        <v>45996</v>
+      </c>
+      <c r="B63">
+        <v>9.280028047289321</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" s="3">
+        <v>46003</v>
+      </c>
+      <c r="B64">
+        <v>9.23870271267193</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65" s="3">
+        <v>46010</v>
+      </c>
+      <c r="B65">
+        <v>9.169139858557138</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66" s="3">
+        <v>46017</v>
+      </c>
+      <c r="B66">
+        <v>9.104340000719917</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67" s="3">
+        <v>46024</v>
+      </c>
+      <c r="B67">
+        <v>9.009624360444363</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68" s="3">
+        <v>46031</v>
+      </c>
+      <c r="B68">
+        <v>8.938316873579137</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69" s="3">
+        <v>46038</v>
+      </c>
+      <c r="B69">
+        <v>8.934572645162575</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70" s="3">
+        <v>46045</v>
+      </c>
+      <c r="B70">
+        <v>8.943667139251048</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71" s="3">
+        <v>46052</v>
+      </c>
+      <c r="B71">
+        <v>9.066807559063221</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72" s="3">
+        <v>46059</v>
+      </c>
+      <c r="B72">
+        <v>9.120360747483794</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73" s="3">
+        <v>46066</v>
+      </c>
+      <c r="B73">
+        <v>9.287553915227601</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" s="3">
+        <v>46073</v>
+      </c>
+      <c r="B74">
+        <v>9.381669394762952</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" s="3">
+        <v>46080</v>
+      </c>
+      <c r="B75">
+        <v>9.401314274777206</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" s="3">
+        <v>46087</v>
+      </c>
+      <c r="B76">
+        <v>9.485507282795416</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" s="3">
+        <v>46094</v>
+      </c>
+      <c r="B77">
+        <v>9.60828357968423</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" s="3">
+        <v>46101</v>
+      </c>
+      <c r="B78">
+        <v>9.600917630100469</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" s="3">
+        <v>46108</v>
+      </c>
+      <c r="B79">
+        <v>9.620762011901764</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" s="3">
+        <v>46115</v>
+      </c>
+      <c r="B80">
+        <v>9.621628384537784</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" s="3">
+        <v>46122</v>
+      </c>
+      <c r="B81">
+        <v>9.603923574675512</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82" s="3">
+        <v>46129</v>
+      </c>
+      <c r="B82">
+        <v>9.640430039898321</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83" s="3">
+        <v>46136</v>
+      </c>
+      <c r="B83">
+        <v>9.506854606995098</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84" s="3">
+        <v>46143</v>
+      </c>
+      <c r="B84">
+        <v>9.438414705092534</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85" s="3">
+        <v>46150</v>
+      </c>
+      <c r="B85">
+        <v>9.287351478369606</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86" s="3">
+        <v>46157</v>
+      </c>
+      <c r="B86">
+        <v>9.189188537106423</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
+      <c r="A87" s="3">
+        <v>46164</v>
+      </c>
+      <c r="B87">
+        <v>9.075670694596599</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
+      <c r="A88" s="3">
+        <v>46171</v>
+      </c>
+      <c r="B88">
+        <v>9.04747586972929</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
+      <c r="A89" s="3">
+        <v>46178</v>
+      </c>
+      <c r="B89">
+        <v>9.044959256931417</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
+      <c r="A90" s="3">
+        <v>46185</v>
+      </c>
+      <c r="B90">
+        <v>9.018700964062976</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
+      <c r="A91" s="3">
+        <v>46192</v>
+      </c>
+      <c r="B91">
+        <v>8.998342050122348</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
+      <c r="A92" s="3">
+        <v>46199</v>
+      </c>
+      <c r="B92">
+        <v>9.011037018943231</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
+      <c r="A93" s="3">
+        <v>46206</v>
+      </c>
+      <c r="B93">
+        <v>9.039758046929808</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94" s="3">
+        <v>46213</v>
+      </c>
+      <c r="B94">
+        <v>9.060211971029302</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
+      <c r="A95" s="3">
+        <v>46220</v>
+      </c>
+      <c r="B95">
+        <v>9.060823312190166</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
+      <c r="A96" s="3">
+        <v>46227</v>
+      </c>
+      <c r="B96">
+        <v>9.050380006660685</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
+      <c r="A97" s="3">
+        <v>46234</v>
+      </c>
+      <c r="B97">
+        <v>9.039311722652332</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98" s="3">
+        <v>46241</v>
+      </c>
+      <c r="B98">
+        <v>9.043856788649268</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99" s="3">
+        <v>46248</v>
+      </c>
+      <c r="B99">
+        <v>9.053504462961257</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100" s="3">
+        <v>46255</v>
+      </c>
+      <c r="B100">
+        <v>9.061990291990012</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101" s="3">
+        <v>46262</v>
+      </c>
+      <c r="B101">
+        <v>9.078716244231492</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102" s="3">
+        <v>46269</v>
+      </c>
+      <c r="B102">
+        <v>9.062834895714907</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103" s="3">
+        <v>46276</v>
+      </c>
+      <c r="B103">
+        <v>9.048972634704064</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104" s="3">
+        <v>46283</v>
+      </c>
+      <c r="B104">
+        <v>9.03488371302417</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B105">
+        <v>9.020844085405651</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106" s="3">
+        <v>46297</v>
+      </c>
+      <c r="B106">
+        <v>8.99891881542902</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107" s="3">
+        <v>46304</v>
+      </c>
+      <c r="B107">
+        <v>8.971268802635894</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108" s="3">
+        <v>46311</v>
+      </c>
+      <c r="B108">
+        <v>8.951751359047446</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109" s="3">
+        <v>46318</v>
+      </c>
+      <c r="B109">
+        <v>8.929949869553599</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110" s="3">
+        <v>46325</v>
+      </c>
+      <c r="B110">
+        <v>8.910354741157116</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111" s="3">
+        <v>46332</v>
+      </c>
+      <c r="B111">
+        <v>8.893010155888447</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112" s="3">
+        <v>46339</v>
+      </c>
+      <c r="B112">
+        <v>8.877203128934486</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113" s="3">
+        <v>46346</v>
+      </c>
+      <c r="B113">
+        <v>8.855589848011618</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114" s="3">
+        <v>46353</v>
+      </c>
+      <c r="B114">
+        <v>8.799668875214097</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115" s="3">
+        <v>46360</v>
+      </c>
+      <c r="B115">
+        <v>8.748033980988737</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116" s="3">
+        <v>46367</v>
+      </c>
+      <c r="B116">
+        <v>8.698223884669115</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117" s="3">
+        <v>46374</v>
+      </c>
+      <c r="B117">
+        <v>8.635253991383156</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118" s="3">
+        <v>46381</v>
+      </c>
+      <c r="B118">
+        <v>8.611460298908582</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119" s="3">
+        <v>46388</v>
+      </c>
+      <c r="B119">
+        <v>8.615117587633545</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120" s="3">
         <v>46395</v>
       </c>
-      <c r="B15">
-        <v>8.485587798963424</v>
+      <c r="B120">
+        <v>8.608362376118839</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121" s="3">
+        <v>46402</v>
+      </c>
+      <c r="B121">
+        <v>8.648128312236496</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.748755364965</v>
+        <v>9.748760278430169</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.724032790702863</v>
+        <v>9.72404359624953</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.72106961911053</v>
+        <v>9.721084526841032</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.70053409296391</v>
+        <v>9.700557806013332</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.705043530506806</v>
+        <v>9.705067000129903</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.698286967984922</v>
+        <v>9.698310142264855</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.694112547751192</v>
+        <v>9.694135830927285</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.708176370489511</v>
+        <v>9.708200225073615</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.720799229032862</v>
+        <v>9.720827198347697</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.727501621078833</v>
+        <v>9.727523216570766</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.736159389620813</v>
+        <v>9.736181251355957</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.712541357586636</v>
+        <v>9.712562767175122</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.668156766051903</v>
+        <v>9.668178276650652</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.63411625358348</v>
+        <v>9.634143101059701</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.600780650332322</v>
+        <v>9.600798615830282</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.562890088939477</v>
+        <v>9.562905733813027</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.505283991007499</v>
+        <v>9.505318022530819</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.433928410877803</v>
+        <v>9.433975910141426</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.357978191070117</v>
+        <v>9.35802254140658</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.290551866342017</v>
+        <v>9.290598440961331</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.267465748122341</v>
+        <v>9.267498245544335</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.280028047289321</v>
+        <v>9.280053139767277</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.23870271267193</v>
+        <v>9.238682179043067</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.169139858557138</v>
+        <v>9.169096359639038</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.104340000719917</v>
+        <v>9.104272747912187</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.009624360444363</v>
+        <v>9.009543396194877</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.938316873579137</v>
+        <v>8.938217215786203</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.934572645162575</v>
+        <v>8.934448580669024</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.943667139251048</v>
+        <v>8.943522660372672</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.066807559063221</v>
+        <v>9.066605212017379</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.120360747483794</v>
+        <v>9.120149184952616</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.287553915227601</v>
+        <v>9.287386444116772</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.381669394762952</v>
+        <v>9.381537946842686</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.401314274777206</v>
+        <v>9.401202426245119</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.485507282795416</v>
+        <v>9.485410700935546</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.60828357968423</v>
+        <v>9.608309109603143</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.600917630100469</v>
+        <v>9.600985639601767</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.620762011901764</v>
+        <v>9.62090393614498</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.621628384537784</v>
+        <v>9.621868109621431</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.603923574675512</v>
+        <v>9.604199245763386</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.640430039898321</v>
+        <v>9.640740996582524</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.506854606995098</v>
+        <v>9.507132384830976</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.438414705092534</v>
+        <v>9.43868045616135</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.287351478369606</v>
+        <v>9.287501920975489</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.189188537106423</v>
+        <v>9.18928459814877</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.075670694596599</v>
+        <v>9.075643435962203</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.04747586972929</v>
+        <v>9.047411615312919</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.044959256931417</v>
+        <v>9.044907680964073</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.018700964062976</v>
+        <v>9.018621637247314</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>8.998342050122348</v>
+        <v>8.998260642035909</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.011037018943231</v>
+        <v>9.010996528312083</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.039758046929808</v>
+        <v>9.039771574912116</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.060211971029302</v>
+        <v>9.060255882219728</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.060823312190166</v>
+        <v>9.060826274971069</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.050380006660685</v>
+        <v>9.050365828753357</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.039311722652332</v>
+        <v>9.039283231644418</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.043856788649268</v>
+        <v>9.043797813097203</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.053504462961257</v>
+        <v>9.053419300829109</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.061990291990012</v>
+        <v>9.061857292074237</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.078716244231492</v>
+        <v>9.07861686546698</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.062834895714907</v>
+        <v>9.062740280405949</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>9.048972634704064</v>
+        <v>9.04885676549859</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>9.03488371302417</v>
+        <v>9.034777785227067</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>9.020844085405651</v>
+        <v>9.020831576198628</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>8.99891881542902</v>
+        <v>8.998990206874694</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>8.971268802635894</v>
+        <v>8.971403103352822</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>8.951751359047446</v>
+        <v>8.95010950621127</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>8.929949869553599</v>
+        <v>8.928431618577644</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>8.910354741157116</v>
+        <v>8.909440815675161</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>8.893010155888447</v>
+        <v>8.891723519901685</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>8.877203128934486</v>
+        <v>8.875581697505293</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>8.855589848011618</v>
+        <v>8.853889137740907</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>8.799668875214097</v>
+        <v>8.7991109712951</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>8.748033980988737</v>
+        <v>8.749080783871602</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>8.698223884669115</v>
+        <v>8.701323235110806</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>8.635253991383156</v>
+        <v>8.640877522621505</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>8.611460298908582</v>
+        <v>8.61930904007281</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>8.615117587633545</v>
+        <v>8.624034124265329</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46395</v>
       </c>
       <c r="B120">
-        <v>8.608362376118839</v>
+        <v>8.620612430692805</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -1354,7 +1354,7 @@
         <v>46402</v>
       </c>
       <c r="B121">
-        <v>8.648128312236496</v>
+        <v>8.665324156963884</v>
       </c>
     </row>
   </sheetData>
